--- a/data/trending_integrated_20260915_14.xlsx
+++ b/data/trending_integrated_20260915_14.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6310</v>
+        <v>3360</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+29.84%</t>
+          <t>'+29.98%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.54</v>
+        <v>1.34</v>
       </c>
       <c r="E2" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F2" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="G2" t="n">
-        <v>193</v>
+        <v>298</v>
       </c>
       <c r="H2" t="n">
-        <v>3.02</v>
+        <v>1.34</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,38 +595,38 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>4860</v>
+        <v>2585</v>
       </c>
       <c r="K2" t="n">
-        <v>5050</v>
+        <v>2725</v>
       </c>
       <c r="L2" t="n">
-        <v>6310</v>
+        <v>3360</v>
       </c>
       <c r="M2" t="n">
-        <v>4910</v>
+        <v>2690</v>
       </c>
       <c r="N2" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>65322324435</v>
+        <v>119452675375</v>
       </c>
       <c r="P2" t="n">
-        <v>11370</v>
+        <v>5100</v>
       </c>
       <c r="Q2" t="n">
-        <v>3300</v>
+        <v>966</v>
       </c>
       <c r="R2" t="n">
-        <v>-437000</v>
+        <v>-426000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>클래리티 통과 정보 유출 가능성 및 양자 보안 테마 부각, 급등에 따른 목표가 상향 기대.</t>
+          <t>광통신, 양자 관련 테마 급등. 삼성과 4381억 계약 체결 가능성 및 세계 최초 타이틀 언급. 거래량 증가하며 주포 개입 가능성 시사.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['양자보안', '호재', '급등']</t>
+          <t>['광통신', '양자', '삼성 계약']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5230</v>
+        <v>6310</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+29.78%</t>
+          <t>'+29.84%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.31</v>
+        <v>-0.54</v>
       </c>
       <c r="E3" t="n">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="F3" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G3" t="n">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="H3" t="n">
-        <v>2.68</v>
+        <v>3.02</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>4030</v>
+        <v>4860</v>
       </c>
       <c r="K3" t="n">
-        <v>4090</v>
+        <v>5050</v>
       </c>
       <c r="L3" t="n">
-        <v>5230</v>
+        <v>6310</v>
       </c>
       <c r="M3" t="n">
-        <v>4020</v>
+        <v>4910</v>
       </c>
       <c r="N3" t="n">
-        <v>2.99</v>
+        <v>3.56</v>
       </c>
       <c r="O3" t="n">
-        <v>48557742829</v>
+        <v>65373290305</v>
       </c>
       <c r="P3" t="n">
-        <v>8980</v>
+        <v>11370</v>
       </c>
       <c r="Q3" t="n">
-        <v>2795</v>
+        <v>3300</v>
       </c>
       <c r="R3" t="n">
-        <v>-185000</v>
+        <v>-437000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>11월 양자구축 체계 의무화에 따른 PQC, KCMVP 인증 기업으로서의 부각. 양자보안 대장주 등극 기대.</t>
+          <t>양자 보안 테마 상승세. 클래리티 법안 통과 기대감 및 스테이블 코인 대장주 부상 가능성 언급. 단주 거래 통한 세력 의심.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['양자보안', 'PQC', 'KCMVP']</t>
+          <t>['양자보안', '클래리티법안', '스테이블코인']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,43 +735,43 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>054920</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3350</v>
+        <v>5230</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+29.59%</t>
+          <t>'+29.78%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.34</v>
+        <v>-0.31</v>
       </c>
       <c r="E4" t="n">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="F4" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G4" t="n">
-        <v>280</v>
+        <v>143</v>
       </c>
       <c r="H4" t="n">
-        <v>1.34</v>
+        <v>2.68</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2585</v>
+        <v>4030</v>
       </c>
       <c r="K4" t="n">
-        <v>2725</v>
+        <v>4090</v>
       </c>
       <c r="L4" t="n">
-        <v>3350</v>
+        <v>5230</v>
       </c>
       <c r="M4" t="n">
-        <v>2690</v>
+        <v>4020</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O4" t="n">
-        <v>113496951055</v>
+        <v>48567726899</v>
       </c>
       <c r="P4" t="n">
-        <v>5100</v>
+        <v>8980</v>
       </c>
       <c r="Q4" t="n">
-        <v>966</v>
+        <v>2795</v>
       </c>
       <c r="R4" t="n">
-        <v>-426000</v>
+        <v>-185000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>삼성과의 대규모 계약 체결 사실 언급. 광통신 및 양자 관련 테마주로 부각되며 급등 기대.</t>
+          <t>11월 양자구축 체계 의무화에 따른 PQC, KCMVP 인증 기업으로서의 부각. 양자보안 대장주 등극 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['계약체결', '광통신', '양자']</t>
+          <t>['양자보안', 'PQC', 'KCMVP']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>062970</t>
+          <t>054920</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11160</v>
+        <v>11380</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+20.39%</t>
+          <t>'+22.76%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.06</v>
       </c>
       <c r="E5" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F5" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G5" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H5" t="n">
         <v>1.19</v>
@@ -886,7 +886,7 @@
         <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>179942862125</v>
+        <v>185628384180</v>
       </c>
       <c r="P5" t="n">
         <v>25050</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>신규 파이프라인 및 특허 기반의 고가 목표 제시. "세계 최초" 타이틀 언급.</t>
+          <t>싸이모신 알파1 관련 세계 최초 타이틀 및 노보노디스크 협력 기대감. 품절주로 분류되며, 월 1회 제형 기술에 대한 관심 집중. 목표가 30만 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['신규파이프라인', '특허', '세계최초']</t>
+          <t>['싸이모신알파1', '품절주', '노보노디스크']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24900</v>
+        <v>24700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+13.70%</t>
+          <t>'+12.79%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F6" t="n">
         <v>61</v>
       </c>
       <c r="G6" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="H6" t="n">
         <v>4.9</v>
@@ -978,7 +978,7 @@
         <v>4.89</v>
       </c>
       <c r="O6" t="n">
-        <v>210936917525</v>
+        <v>214302176425</v>
       </c>
       <c r="P6" t="n">
         <v>50600</v>
@@ -1023,70 +1023,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>현대제철</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>35300</v>
+        <v>3615</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.97%</t>
+          <t>'+6.32%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.13</v>
+        <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F7" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G7" t="n">
-        <v>302</v>
+        <v>206</v>
       </c>
       <c r="H7" t="n">
-        <v>14.93</v>
+        <v>0.83</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>33000</v>
+        <v>3400</v>
       </c>
       <c r="K7" t="n">
-        <v>32750</v>
+        <v>3450</v>
       </c>
       <c r="L7" t="n">
-        <v>37200</v>
+        <v>4080</v>
       </c>
       <c r="M7" t="n">
-        <v>32750</v>
+        <v>3445</v>
       </c>
       <c r="N7" t="n">
-        <v>15.06</v>
+        <v>0.71</v>
       </c>
       <c r="O7" t="n">
-        <v>51586091850</v>
+        <v>149101131020</v>
       </c>
       <c r="P7" t="n">
-        <v>50400</v>
+        <v>4335</v>
       </c>
       <c r="Q7" t="n">
-        <v>23650</v>
+        <v>1246</v>
       </c>
       <c r="R7" t="n">
-        <v>334000</v>
+        <v>120000</v>
       </c>
       <c r="S7" t="n">
-        <v>108000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>PBR 0.22, 0.07 등 저평가 지표와 한국거래소의 저PBR 기업 딱지 관련 뉴스를 바탕으로 상승 기대감이 형성됨. 120일선 돌파 등 기술적 지표도 언급됨.</t>
+          <t>긍정적인 상승 파동 기대감 및 세력 움직임 언급. "날아간다", "대장" 등 긍정적 표현.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['PBR', '저평가', '정배열']</t>
+          <t>['상승파동', '대장', '세력']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,77 +1108,77 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>004020</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>현대제철</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3620</v>
+        <v>34950</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+6.47%</t>
+          <t>'+5.91%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="E8" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F8" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="G8" t="n">
-        <v>199</v>
+        <v>304</v>
       </c>
       <c r="H8" t="n">
-        <v>0.83</v>
+        <v>14.93</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>3400</v>
+        <v>33000</v>
       </c>
       <c r="K8" t="n">
-        <v>3450</v>
+        <v>32750</v>
       </c>
       <c r="L8" t="n">
-        <v>4080</v>
+        <v>37200</v>
       </c>
       <c r="M8" t="n">
-        <v>3445</v>
+        <v>32750</v>
       </c>
       <c r="N8" t="n">
-        <v>0.71</v>
+        <v>15.06</v>
       </c>
       <c r="O8" t="n">
-        <v>148524867564</v>
+        <v>52375590775</v>
       </c>
       <c r="P8" t="n">
-        <v>4335</v>
+        <v>50400</v>
       </c>
       <c r="Q8" t="n">
-        <v>1246</v>
+        <v>23650</v>
       </c>
       <c r="R8" t="n">
-        <v>120000</v>
+        <v>334000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>108000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>긍정적인 상승 파동 기대감 및 세력 움직임 언급. "날아간다", "대장" 등 긍정적 표현.</t>
+          <t>PBR 0.22, 0.07 등 저평가 지표와 한국거래소의 저PBR 기업 딱지 관련 뉴스를 바탕으로 상승 기대감이 형성됨. 120일선 돌파 등 기술적 지표도 언급됨.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['상승파동', '대장', '세력']</t>
+          <t>['PBR', '저평가', '정배열']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>004020</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50400</v>
+        <v>50000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.44%</t>
+          <t>'+4.60%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.18</v>
       </c>
       <c r="E9" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F9" t="n">
         <v>97</v>
       </c>
       <c r="G9" t="n">
-        <v>583</v>
+        <v>592</v>
       </c>
       <c r="H9" t="n">
         <v>13.97</v>
@@ -1254,7 +1254,7 @@
         <v>14.15</v>
       </c>
       <c r="O9" t="n">
-        <v>85410018325</v>
+        <v>87340200875</v>
       </c>
       <c r="P9" t="n">
         <v>108900</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31750</v>
+        <v>31650</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.61%</t>
+          <t>'+4.28%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F10" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G10" t="n">
-        <v>874</v>
+        <v>884</v>
       </c>
       <c r="H10" t="n">
         <v>17.5</v>
@@ -1346,7 +1346,7 @@
         <v>17.55</v>
       </c>
       <c r="O10" t="n">
-        <v>13970806275</v>
+        <v>14303861000</v>
       </c>
       <c r="P10" t="n">
         <v>69200</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>HLB, FDA 승인 기대감 속 개인 투자자 혼조세. 부정적 전망과 긍정적 기대가 공존하며 혼조세.</t>
+          <t>담관암 FDA 승인 관련 기대와 CRL 공시로 인한 실망감 공존. 기관 외인 매도세 관찰되며, 이유 없는 급락에 대한 분석 요구.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['FDA 승인', '담관암']</t>
+          <t>['담관암', 'FDA승인', 'CRL']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14700</v>
+        <v>141400</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+4.18%</t>
+          <t>'+3.44%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="F11" t="n">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="G11" t="n">
-        <v>192</v>
+        <v>329</v>
       </c>
       <c r="H11" t="n">
-        <v>10.75</v>
+        <v>15.81</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,47 +1423,47 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>14110</v>
+        <v>136700</v>
       </c>
       <c r="K11" t="n">
-        <v>14110</v>
+        <v>139500</v>
       </c>
       <c r="L11" t="n">
-        <v>15250</v>
+        <v>144100</v>
       </c>
       <c r="M11" t="n">
-        <v>13400</v>
+        <v>138200</v>
       </c>
       <c r="N11" t="n">
-        <v>10.69</v>
+        <v>15.76</v>
       </c>
       <c r="O11" t="n">
-        <v>118477083045</v>
+        <v>113105749200</v>
       </c>
       <c r="P11" t="n">
-        <v>23550</v>
+        <v>164700</v>
       </c>
       <c r="Q11" t="n">
-        <v>5700</v>
+        <v>87700</v>
       </c>
       <c r="R11" t="n">
-        <v>-116000</v>
+        <v>2000</v>
       </c>
       <c r="S11" t="n">
-        <v>130000</v>
+        <v>39000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>거래량 증가와 함께 15000원 돌파 시도, 주포 움직임에 대한 기대와 우려 혼재.</t>
+          <t>합병 반대 목소리와 함께 정유 및 배터리 업황 호조 기대. 주가 급락 및 상승 가능성 혼재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주포', '거래량', '15000원']</t>
+          <t>['합병반대', '정유', '배터리']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1471,82 +1471,82 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>142400</v>
+        <v>15090</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+4.17%</t>
+          <t>'+2.93%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.05</v>
+        <v>-1.17</v>
       </c>
       <c r="E12" t="n">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="F12" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="G12" t="n">
-        <v>324</v>
+        <v>372</v>
       </c>
       <c r="H12" t="n">
-        <v>15.81</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>136700</v>
+        <v>14660</v>
       </c>
       <c r="K12" t="n">
-        <v>139500</v>
+        <v>14980</v>
       </c>
       <c r="L12" t="n">
-        <v>144100</v>
+        <v>15460</v>
       </c>
       <c r="M12" t="n">
-        <v>138200</v>
+        <v>14330</v>
       </c>
       <c r="N12" t="n">
-        <v>15.76</v>
+        <v>1.17</v>
       </c>
       <c r="O12" t="n">
-        <v>111063991550</v>
+        <v>54550761575</v>
       </c>
       <c r="P12" t="n">
-        <v>164700</v>
+        <v>36200</v>
       </c>
       <c r="Q12" t="n">
-        <v>87700</v>
+        <v>8920</v>
       </c>
       <c r="R12" t="n">
-        <v>2000</v>
+        <v>-13000</v>
       </c>
       <c r="S12" t="n">
-        <v>39000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>합병 반대 목소리와 함께 정유 및 배터리 업황 호조 기대. 주가 급락 및 상승 가능성 혼재.</t>
+          <t>유가 상승 및 이란 관련 뉴스 언급. 4배 상승 기대감과 함께 외인 유입 및 장난질 가능성 언급. 3~5% 상승 메리트 부족 지적.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['합병반대', '정유', '배터리']</t>
+          <t>['유가', '이란', '외인']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,182 +1568,182 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17620</v>
+        <v>14500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.44%</t>
+          <t>'+2.76%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-2.35</v>
+        <v>0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>204</v>
+        <v>59</v>
       </c>
       <c r="F13" t="n">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="G13" t="n">
-        <v>297</v>
+        <v>195</v>
       </c>
       <c r="H13" t="n">
-        <v>0.35</v>
+        <v>10.75</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>17200</v>
+        <v>14110</v>
       </c>
       <c r="K13" t="n">
-        <v>17220</v>
+        <v>14110</v>
       </c>
       <c r="L13" t="n">
-        <v>18390</v>
+        <v>15250</v>
       </c>
       <c r="M13" t="n">
-        <v>16600</v>
+        <v>13400</v>
       </c>
       <c r="N13" t="n">
-        <v>2.7</v>
+        <v>10.69</v>
       </c>
       <c r="O13" t="n">
-        <v>186755005415</v>
+        <v>119763024730</v>
       </c>
       <c r="P13" t="n">
-        <v>30550</v>
+        <v>23550</v>
       </c>
       <c r="Q13" t="n">
-        <v>6100</v>
+        <v>5700</v>
       </c>
       <c r="R13" t="n">
-        <v>-32000</v>
+        <v>-116000</v>
       </c>
       <c r="S13" t="n">
-        <v>3000</v>
+        <v>130000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 양자 보안주 폭등 및 세계 최초 타이틀 기반 신고가 경신.</t>
+          <t>거래량 증가와 함께 15000원 돌파 시도, 주포 움직임에 대한 기대와 우려 혼재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['양자 보안', '세계 최초', '신고가']</t>
+          <t>['주포', '거래량', '15000원']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>093370</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10490</v>
+        <v>17590</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.14%</t>
+          <t>'+2.27%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.26</v>
+        <v>-2.35</v>
       </c>
       <c r="E14" t="n">
-        <v>177</v>
+        <v>207</v>
       </c>
       <c r="F14" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="G14" t="n">
-        <v>436</v>
+        <v>297</v>
       </c>
       <c r="H14" t="n">
-        <v>17.93</v>
+        <v>0.35</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>10270</v>
+        <v>17200</v>
       </c>
       <c r="K14" t="n">
-        <v>11000</v>
+        <v>17220</v>
       </c>
       <c r="L14" t="n">
-        <v>11650</v>
+        <v>18390</v>
       </c>
       <c r="M14" t="n">
-        <v>10010</v>
+        <v>16600</v>
       </c>
       <c r="N14" t="n">
-        <v>17.67</v>
+        <v>2.7</v>
       </c>
       <c r="O14" t="n">
-        <v>335631044655</v>
+        <v>188179777275</v>
       </c>
       <c r="P14" t="n">
-        <v>22450</v>
+        <v>30550</v>
       </c>
       <c r="Q14" t="n">
-        <v>1760</v>
+        <v>6100</v>
       </c>
       <c r="R14" t="n">
-        <v>139000</v>
+        <v>-32000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>아이온큐 급등과 트럼프 AI 정책 강화에 따른 광통신 대장주로서의 기대감. 기타법인 매수세 유입 확인.</t>
+          <t>미국 양자 보안주 폭등 및 세계 최초 타이틀 기반 신고가 경신.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '기타법인']</t>
+          <t>['양자 보안', '세계 최초', '신고가']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,77 +1752,77 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14970</v>
+        <v>10470</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.11%</t>
+          <t>'+1.95%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-1.17</v>
+        <v>0.26</v>
       </c>
       <c r="E15" t="n">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="F15" t="n">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="G15" t="n">
-        <v>374</v>
+        <v>440</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>17.93</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>14660</v>
+        <v>10270</v>
       </c>
       <c r="K15" t="n">
-        <v>14980</v>
+        <v>11000</v>
       </c>
       <c r="L15" t="n">
-        <v>15460</v>
+        <v>11650</v>
       </c>
       <c r="M15" t="n">
-        <v>14330</v>
+        <v>10010</v>
       </c>
       <c r="N15" t="n">
-        <v>1.17</v>
+        <v>17.67</v>
       </c>
       <c r="O15" t="n">
-        <v>53642783515</v>
+        <v>337903780065</v>
       </c>
       <c r="P15" t="n">
-        <v>36200</v>
+        <v>22450</v>
       </c>
       <c r="Q15" t="n">
-        <v>8920</v>
+        <v>1760</v>
       </c>
       <c r="R15" t="n">
-        <v>-13000</v>
+        <v>139000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>유가 상승 및 이란 관련 뉴스 언급. 4배 상승 기대감과 함께 외인 유입 및 장난질 가능성 언급. 3~5% 상승 메리트 부족 지적.</t>
+          <t>아이온큐 급등 및 트럼프 AI 정책 기대감 반영. 기타법인 매수세 유입. 광통신 테마와 연관성 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['유가', '이란', '외인']</t>
+          <t>['아이온큐', 'AI', '기타법인']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19120</v>
+        <v>10110</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.92%</t>
+          <t>'+1.20%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="F16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G16" t="n">
-        <v>400</v>
+        <v>144</v>
       </c>
       <c r="H16" t="n">
-        <v>10.53</v>
+        <v>0.6</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,38 +1883,38 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>18760</v>
+        <v>9990</v>
       </c>
       <c r="K16" t="n">
-        <v>18440</v>
+        <v>10110</v>
       </c>
       <c r="L16" t="n">
-        <v>19330</v>
+        <v>11390</v>
       </c>
       <c r="M16" t="n">
-        <v>18120</v>
+        <v>9980</v>
       </c>
       <c r="N16" t="n">
-        <v>10.55</v>
+        <v>0.6</v>
       </c>
       <c r="O16" t="n">
-        <v>66712731545</v>
+        <v>156403663265</v>
       </c>
       <c r="P16" t="n">
-        <v>40350</v>
+        <v>15960</v>
       </c>
       <c r="Q16" t="n">
-        <v>3320</v>
+        <v>3500</v>
       </c>
       <c r="R16" t="n">
-        <v>6000</v>
+        <v>1000</v>
       </c>
       <c r="S16" t="n">
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>긍정적인 흐름과 대박 공시 기대감 형성. "대차해지" 독려 운동 활발.</t>
+          <t>부정적인 언급과 함께 주가 조작 의혹 제기. "저질약품", "최악" 등 부정적 표현 다수.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['대차해지', '공시', '흐름']</t>
+          <t>['주가조작', '저질약품']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10060</v>
+        <v>18910</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.70%</t>
+          <t>'+0.80%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="E17" t="n">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="F17" t="n">
         <v>50</v>
       </c>
       <c r="G17" t="n">
-        <v>140</v>
+        <v>404</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6</v>
+        <v>10.53</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,38 +1975,38 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>9990</v>
+        <v>18760</v>
       </c>
       <c r="K17" t="n">
-        <v>10110</v>
+        <v>18440</v>
       </c>
       <c r="L17" t="n">
-        <v>11390</v>
+        <v>19330</v>
       </c>
       <c r="M17" t="n">
-        <v>9980</v>
+        <v>18120</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6</v>
+        <v>10.55</v>
       </c>
       <c r="O17" t="n">
-        <v>155977440450</v>
+        <v>68464701710</v>
       </c>
       <c r="P17" t="n">
-        <v>15960</v>
+        <v>40350</v>
       </c>
       <c r="Q17" t="n">
-        <v>3500</v>
+        <v>3320</v>
       </c>
       <c r="R17" t="n">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>부정적인 언급과 함께 주가 조작 의혹 제기. "저질약품", "최악" 등 부정적 표현 다수.</t>
+          <t>긍정적인 흐름과 대박 공시 기대감 형성. "대차해지" 독려 운동 활발.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주가조작', '저질약품']</t>
+          <t>['대차해지', '공시', '흐름']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6880</v>
+        <v>6930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-0.29%</t>
+          <t>'+0.43%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.97</v>
       </c>
       <c r="E18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F18" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G18" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H18" t="n">
         <v>0.7</v>
@@ -2082,7 +2082,7 @@
         <v>1.67</v>
       </c>
       <c r="O18" t="n">
-        <v>44631492915</v>
+        <v>44862096045</v>
       </c>
       <c r="P18" t="n">
         <v>10360</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>248000</v>
+        <v>247000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-0.40%</t>
+          <t>'-0.80%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G19" t="n">
-        <v>1560</v>
+        <v>1515</v>
       </c>
       <c r="H19" t="n">
         <v>46.57</v>
@@ -2174,7 +2174,7 @@
         <v>46.64</v>
       </c>
       <c r="O19" t="n">
-        <v>1916226564500</v>
+        <v>1953344501000</v>
       </c>
       <c r="P19" t="n">
         <v>374500</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>증시 안정 및 금리 인상 선반영 기대감 속 차트 분석 및 투자 심리 언급.</t>
+          <t>시장 안정화 언급에도 불구하고 정치적 언급 및 게시판 불편함 토로. 금리 인상 선반영 및 특별배당 기대감 존재.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['증시', '금리인상', '차트']</t>
+          <t>['금리인상', '특별배당', '정치']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1688000</v>
+        <v>1680000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-0.53%</t>
+          <t>'-1.00%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2237,10 +2237,10 @@
         <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="G20" t="n">
-        <v>1632</v>
+        <v>1628</v>
       </c>
       <c r="H20" t="n">
         <v>50.27</v>
@@ -2260,13 +2260,13 @@
         <v>1729000</v>
       </c>
       <c r="M20" t="n">
-        <v>1685000</v>
+        <v>1680000</v>
       </c>
       <c r="N20" t="n">
         <v>50.47</v>
       </c>
       <c r="O20" t="n">
-        <v>3239473860000</v>
+        <v>3348848076500</v>
       </c>
       <c r="P20" t="n">
         <v>2987000</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>기관 수급에 따른 단기 반등에도 AI 이슈, 금리, 중국 메모리 등 다양한 변수에 대한 부정적 전망.</t>
+          <t>AI 이슈 및 트럼프 발언에 따른 주가 변동성 관찰. 금리, 중국 메모리 등 다양한 이슈 언급. 투자 리스크보다 투자 안 하는 리스크가 크다는 의견.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['AI', '기관수급', '금리']</t>
+          <t>['AI', '트럼프', '금리']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>223000</v>
+        <v>222000</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-0.89%</t>
+          <t>'-1.33%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.15</v>
       </c>
       <c r="E21" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="F21" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G21" t="n">
-        <v>950</v>
+        <v>958</v>
       </c>
       <c r="H21" t="n">
         <v>7.2</v>
@@ -2358,7 +2358,7 @@
         <v>7.05</v>
       </c>
       <c r="O21" t="n">
-        <v>88935242000</v>
+        <v>89525116250</v>
       </c>
       <c r="P21" t="n">
         <v>426000</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8690</v>
+        <v>8670</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-1.81%</t>
+          <t>'-2.03%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="F22" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G22" t="n">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="H22" t="n">
         <v>27.16</v>
@@ -2444,13 +2444,13 @@
         <v>8840</v>
       </c>
       <c r="M22" t="n">
-        <v>8670</v>
+        <v>8660</v>
       </c>
       <c r="N22" t="n">
         <v>27.16</v>
       </c>
       <c r="O22" t="n">
-        <v>21470600945</v>
+        <v>22645549770</v>
       </c>
       <c r="P22" t="n">
         <v>17950</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>실적 부진 및 대표 사퇴 요구 등 부정적 여론 형성. 목표주가 하향 조정 및 적자 지속 우려.</t>
+          <t>목표주가 상향 조정에도 불구하고 주가 부진 지속. 연기금 순매수세 관찰되나, 컨센서스 하회 및 실적 부진에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['실적부진', '목표주가', '적자']</t>
+          <t>['목표주가', '실적부진', '연기금']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -2495,79 +2495,79 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>85000</v>
+        <v>14100</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-2.30%</t>
+          <t>'-2.69%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="E23" t="n">
-        <v>222</v>
+        <v>113</v>
       </c>
       <c r="F23" t="n">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="G23" t="n">
-        <v>855</v>
+        <v>499</v>
       </c>
       <c r="H23" t="n">
-        <v>23.45</v>
+        <v>1.8</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>87000</v>
+        <v>14490</v>
       </c>
       <c r="K23" t="n">
-        <v>86200</v>
+        <v>14410</v>
       </c>
       <c r="L23" t="n">
-        <v>86800</v>
+        <v>14600</v>
       </c>
       <c r="M23" t="n">
-        <v>85000</v>
+        <v>13930</v>
       </c>
       <c r="N23" t="n">
-        <v>23.56</v>
+        <v>1.88</v>
       </c>
       <c r="O23" t="n">
-        <v>113584374450</v>
+        <v>59952711865</v>
       </c>
       <c r="P23" t="n">
-        <v>139200</v>
+        <v>31500</v>
       </c>
       <c r="Q23" t="n">
-        <v>57000</v>
+        <v>1272</v>
       </c>
       <c r="R23" t="n">
-        <v>-153000</v>
+        <v>99000</v>
       </c>
       <c r="S23" t="n">
-        <v>-121000</v>
+        <v>-4000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>두산에너빌리티는 원전 사업 관련 긍정적 언급과 함께 엑스에너지의 급등세를 기반으로 주가 상승을 기대하는 글들이 일부 있었다. 그러나 전날의 과도한 하락에 대한 언급도 존재한다.</t>
+          <t>언론 홍보 효과 및 지지 구간 언급. AI, 광전자 관련 테마주로 긍정적 전망.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['원전', '엑스에너지', '주가 상승']</t>
+          <t>['언론홍보', '광통신', 'AI']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2575,91 +2575,91 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14120</v>
+        <v>84600</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-2.55%</t>
+          <t>'-2.76%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="E24" t="n">
-        <v>111</v>
+        <v>235</v>
       </c>
       <c r="F24" t="n">
-        <v>62</v>
+        <v>132</v>
       </c>
       <c r="G24" t="n">
-        <v>493</v>
+        <v>873</v>
       </c>
       <c r="H24" t="n">
-        <v>1.8</v>
+        <v>23.45</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>14490</v>
+        <v>87000</v>
       </c>
       <c r="K24" t="n">
-        <v>14410</v>
+        <v>86200</v>
       </c>
       <c r="L24" t="n">
-        <v>14600</v>
+        <v>86800</v>
       </c>
       <c r="M24" t="n">
-        <v>13930</v>
+        <v>84600</v>
       </c>
       <c r="N24" t="n">
-        <v>1.88</v>
+        <v>23.56</v>
       </c>
       <c r="O24" t="n">
-        <v>58883154780</v>
+        <v>118037342600</v>
       </c>
       <c r="P24" t="n">
-        <v>31500</v>
+        <v>139200</v>
       </c>
       <c r="Q24" t="n">
-        <v>1272</v>
+        <v>57000</v>
       </c>
       <c r="R24" t="n">
-        <v>99000</v>
+        <v>-153000</v>
       </c>
       <c r="S24" t="n">
-        <v>-4000</v>
+        <v>-121000</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>언론 홍보 효과 및 지지 구간 언급. AI, 광전자 관련 테마주로 긍정적 전망.</t>
+          <t>두산에너빌리티는 원전 사업 관련 긍정적 언급과 함께 엑스에너지의 급등세를 기반으로 주가 상승을 기대하는 글들이 일부 있었다. 그러나 전날의 과도한 하락에 대한 언급도 존재한다.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['언론홍보', '광통신', 'AI']</t>
+          <t>['원전', '엑스에너지', '주가 상승']</t>
         </is>
       </c>
       <c r="X24" t="n">
@@ -2667,12 +2667,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -2683,11 +2683,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4115</v>
+        <v>4090</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-4.86%</t>
+          <t>'-5.43%</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -2700,7 +2700,7 @@
         <v>45</v>
       </c>
       <c r="G25" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H25" t="n">
         <v>0.77</v>
@@ -2726,7 +2726,7 @@
         <v>0.59</v>
       </c>
       <c r="O25" t="n">
-        <v>70238603917</v>
+        <v>71532391711</v>
       </c>
       <c r="P25" t="n">
         <v>8100</v>
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>20850</v>
+        <v>20800</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-5.66%</t>
+          <t>'-5.88%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.09</v>
       </c>
       <c r="E26" t="n">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="F26" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G26" t="n">
-        <v>521</v>
+        <v>534</v>
       </c>
       <c r="H26" t="n">
         <v>28.9</v>
@@ -2818,7 +2818,7 @@
         <v>28.81</v>
       </c>
       <c r="O26" t="n">
-        <v>67035728425</v>
+        <v>68101496425</v>
       </c>
       <c r="P26" t="n">
         <v>35350</v>
@@ -2834,16 +2834,16 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>12억 달러 수주 공시에도 주가 하락, 시장 반응에 대한 불만과 수주 악재 해석.</t>
+          <t>12억 달러 수주 공시에도 주가 하락. 시장은 수주를 악재로 인식하며, 공매도 및 기타 법인 매도세 관찰됨. 자사주 소각 등 주가 부양책 요구.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['수주', '공시', '주가']</t>
+          <t>['수주공시', '주가하락', '공매도']</t>
         </is>
       </c>
       <c r="X26" t="n">

--- a/data/trending_integrated_20260915_14.xlsx
+++ b/data/trending_integrated_20260915_14.xlsx
@@ -578,13 +578,13 @@
         <v>1.34</v>
       </c>
       <c r="E2" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G2" t="n">
-        <v>298</v>
+        <v>326</v>
       </c>
       <c r="H2" t="n">
         <v>1.34</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>119452675375</v>
+        <v>119928138895</v>
       </c>
       <c r="P2" t="n">
         <v>5100</v>
@@ -619,23 +619,23 @@
         <v>966</v>
       </c>
       <c r="R2" t="n">
-        <v>-426000</v>
+        <v>-389000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>광통신, 양자 관련 테마 급등. 삼성과 4381억 계약 체결 가능성 및 세계 최초 타이틀 언급. 거래량 증가하며 주포 개입 가능성 시사.</t>
+          <t>삼성과 4381억 계약 체결 확인. 광통신, 양자 관련 테마로 급등세. 주포 개입 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광통신', '양자', '삼성 계약']</t>
+          <t>['삼성', '광통신', '양자']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -676,7 +676,7 @@
         <v>64</v>
       </c>
       <c r="G3" t="n">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="H3" t="n">
         <v>3.02</v>
@@ -702,7 +702,7 @@
         <v>3.56</v>
       </c>
       <c r="O3" t="n">
-        <v>65373290305</v>
+        <v>65517183545</v>
       </c>
       <c r="P3" t="n">
         <v>11370</v>
@@ -711,23 +711,23 @@
         <v>3300</v>
       </c>
       <c r="R3" t="n">
-        <v>-437000</v>
+        <v>-439000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>양자 보안 테마 상승세. 클래리티 법안 통과 기대감 및 스테이블 코인 대장주 부상 가능성 언급. 단주 거래 통한 세력 의심.</t>
+          <t>양자 보안 테마 강세. 클래리티 법안 통과 여부가 주가에 영향을 줄 것으로 예상. 10000원 돌파 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['양자보안', '클래리티법안', '스테이블코인']</t>
+          <t>['양자보안', '클래리티', '법안']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -768,7 +768,7 @@
         <v>57</v>
       </c>
       <c r="G4" t="n">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="H4" t="n">
         <v>2.68</v>
@@ -794,7 +794,7 @@
         <v>2.99</v>
       </c>
       <c r="O4" t="n">
-        <v>48567726899</v>
+        <v>48574572969</v>
       </c>
       <c r="P4" t="n">
         <v>8980</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11380</v>
+        <v>11270</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+22.76%</t>
+          <t>'+21.57%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.06</v>
       </c>
       <c r="E5" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F5" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G5" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="H5" t="n">
         <v>1.19</v>
@@ -886,7 +886,7 @@
         <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>185628384180</v>
+        <v>189488045760</v>
       </c>
       <c r="P5" t="n">
         <v>25050</v>
@@ -895,23 +895,23 @@
         <v>3705</v>
       </c>
       <c r="R5" t="n">
-        <v>-44000</v>
+        <v>-31000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>싸이모신 알파1 관련 세계 최초 타이틀 및 노보노디스크 협력 기대감. 품절주로 분류되며, 월 1회 제형 기술에 대한 관심 집중. 목표가 30만 언급.</t>
+          <t>탈모 치료제 및 장기지속형 주사제 관련 특허 및 개발 기대감. 품절주 및 목표가 30만 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['싸이모신알파1', '품절주', '노보노디스크']</t>
+          <t>['탈모치료제', '장기지속형주사제', '특허']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24700</v>
+        <v>24750</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+12.79%</t>
+          <t>'+13.01%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G6" t="n">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="H6" t="n">
         <v>4.9</v>
@@ -978,7 +978,7 @@
         <v>4.89</v>
       </c>
       <c r="O6" t="n">
-        <v>214302176425</v>
+        <v>217245534050</v>
       </c>
       <c r="P6" t="n">
         <v>50600</v>
@@ -990,7 +990,7 @@
         <v>-1000</v>
       </c>
       <c r="S6" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1023,70 +1023,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>현대제철</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3615</v>
+        <v>34950</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.32%</t>
+          <t>'+5.91%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="E7" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F7" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
-        <v>206</v>
+        <v>308</v>
       </c>
       <c r="H7" t="n">
-        <v>0.83</v>
+        <v>14.93</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3400</v>
+        <v>33000</v>
       </c>
       <c r="K7" t="n">
-        <v>3450</v>
+        <v>32750</v>
       </c>
       <c r="L7" t="n">
-        <v>4080</v>
+        <v>37200</v>
       </c>
       <c r="M7" t="n">
-        <v>3445</v>
+        <v>32750</v>
       </c>
       <c r="N7" t="n">
-        <v>0.71</v>
+        <v>15.06</v>
       </c>
       <c r="O7" t="n">
-        <v>149101131020</v>
+        <v>53142455775</v>
       </c>
       <c r="P7" t="n">
-        <v>4335</v>
+        <v>50400</v>
       </c>
       <c r="Q7" t="n">
-        <v>1246</v>
+        <v>23650</v>
       </c>
       <c r="R7" t="n">
-        <v>120000</v>
+        <v>349000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>109000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>긍정적인 상승 파동 기대감 및 세력 움직임 언급. "날아간다", "대장" 등 긍정적 표현.</t>
+          <t>PBR 0.22, 0.07 등 저평가 지표와 한국거래소의 저PBR 기업 딱지 관련 뉴스를 바탕으로 상승 기대감이 형성됨. 120일선 돌파 등 기술적 지표도 언급됨.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['상승파동', '대장', '세력']</t>
+          <t>['PBR', '저평가', '정배열']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,77 +1108,77 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>004020</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>현대제철</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>34950</v>
+        <v>3585</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.91%</t>
+          <t>'+5.44%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.13</v>
+        <v>0.12</v>
       </c>
       <c r="E8" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F8" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G8" t="n">
-        <v>304</v>
+        <v>211</v>
       </c>
       <c r="H8" t="n">
-        <v>14.93</v>
+        <v>0.83</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>33000</v>
+        <v>3400</v>
       </c>
       <c r="K8" t="n">
-        <v>32750</v>
+        <v>3450</v>
       </c>
       <c r="L8" t="n">
-        <v>37200</v>
+        <v>4080</v>
       </c>
       <c r="M8" t="n">
-        <v>32750</v>
+        <v>3445</v>
       </c>
       <c r="N8" t="n">
-        <v>15.06</v>
+        <v>0.71</v>
       </c>
       <c r="O8" t="n">
-        <v>52375590775</v>
+        <v>150601114122</v>
       </c>
       <c r="P8" t="n">
-        <v>50400</v>
+        <v>4335</v>
       </c>
       <c r="Q8" t="n">
-        <v>23650</v>
+        <v>1246</v>
       </c>
       <c r="R8" t="n">
-        <v>334000</v>
+        <v>-32000</v>
       </c>
       <c r="S8" t="n">
-        <v>108000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>PBR 0.22, 0.07 등 저평가 지표와 한국거래소의 저PBR 기업 딱지 관련 뉴스를 바탕으로 상승 기대감이 형성됨. 120일선 돌파 등 기술적 지표도 언급됨.</t>
+          <t>긍정적인 상승 파동 기대감 및 세력 움직임 언급. "날아간다", "대장" 등 긍정적 표현.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['PBR', '저평가', '정배열']</t>
+          <t>['상승파동', '대장', '세력']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,86 +1200,86 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>004020</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50000</v>
+        <v>31700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.60%</t>
+          <t>'+4.45%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.18</v>
+        <v>-0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F9" t="n">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="G9" t="n">
-        <v>592</v>
+        <v>890</v>
       </c>
       <c r="H9" t="n">
-        <v>13.97</v>
+        <v>17.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>47800</v>
+        <v>30350</v>
       </c>
       <c r="K9" t="n">
-        <v>47300</v>
+        <v>30250</v>
       </c>
       <c r="L9" t="n">
-        <v>54600</v>
+        <v>32300</v>
       </c>
       <c r="M9" t="n">
-        <v>46400</v>
+        <v>30250</v>
       </c>
       <c r="N9" t="n">
-        <v>14.15</v>
+        <v>17.55</v>
       </c>
       <c r="O9" t="n">
-        <v>87340200875</v>
+        <v>14608817350</v>
       </c>
       <c r="P9" t="n">
-        <v>108900</v>
+        <v>69200</v>
       </c>
       <c r="Q9" t="n">
-        <v>18230</v>
+        <v>24150</v>
       </c>
       <c r="R9" t="n">
-        <v>55000</v>
+        <v>82000</v>
       </c>
       <c r="S9" t="n">
-        <v>56000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>연이은 수주 공시에도 주가 부진, 유상증자 변수 및 공매도 관련 논의.</t>
+          <t>담관암 FDA 승인 관련 기대와 CRL 공시로 인한 실망감 공존. 기관 외인 매도세 관찰되며, 이유 없는 급락에 대한 분석 요구.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['수주', '공시', '유상증자']</t>
+          <t>['담관암', 'FDA승인', 'CRL']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,86 +1292,86 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31650</v>
+        <v>49850</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.28%</t>
+          <t>'+4.29%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.05</v>
+        <v>-0.18</v>
       </c>
       <c r="E10" t="n">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="F10" t="n">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="G10" t="n">
-        <v>884</v>
+        <v>601</v>
       </c>
       <c r="H10" t="n">
-        <v>17.5</v>
+        <v>13.97</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>30350</v>
+        <v>47800</v>
       </c>
       <c r="K10" t="n">
-        <v>30250</v>
+        <v>47300</v>
       </c>
       <c r="L10" t="n">
-        <v>32300</v>
+        <v>54600</v>
       </c>
       <c r="M10" t="n">
-        <v>30250</v>
+        <v>46400</v>
       </c>
       <c r="N10" t="n">
-        <v>17.55</v>
+        <v>14.15</v>
       </c>
       <c r="O10" t="n">
-        <v>14303861000</v>
+        <v>89665845875</v>
       </c>
       <c r="P10" t="n">
-        <v>69200</v>
+        <v>108900</v>
       </c>
       <c r="Q10" t="n">
-        <v>24150</v>
+        <v>18230</v>
       </c>
       <c r="R10" t="n">
-        <v>64000</v>
+        <v>70000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>65000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>담관암 FDA 승인 관련 기대와 CRL 공시로 인한 실망감 공존. 기관 외인 매도세 관찰되며, 이유 없는 급락에 대한 분석 요구.</t>
+          <t>연이은 수주 공시에도 주가 부진, 유상증자 변수 및 공매도 관련 논의.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['담관암', 'FDA승인', 'CRL']</t>
+          <t>['수주', '공시', '유상증자']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>141400</v>
+        <v>15260</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.44%</t>
+          <t>'+4.09%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.05</v>
+        <v>-1.17</v>
       </c>
       <c r="E11" t="n">
-        <v>140</v>
+        <v>187</v>
       </c>
       <c r="F11" t="n">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="G11" t="n">
-        <v>329</v>
+        <v>386</v>
       </c>
       <c r="H11" t="n">
-        <v>15.81</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>136700</v>
+        <v>14660</v>
       </c>
       <c r="K11" t="n">
-        <v>139500</v>
+        <v>14980</v>
       </c>
       <c r="L11" t="n">
-        <v>144100</v>
+        <v>15460</v>
       </c>
       <c r="M11" t="n">
-        <v>138200</v>
+        <v>14330</v>
       </c>
       <c r="N11" t="n">
-        <v>15.76</v>
+        <v>1.17</v>
       </c>
       <c r="O11" t="n">
-        <v>113105749200</v>
+        <v>60506493015</v>
       </c>
       <c r="P11" t="n">
-        <v>164700</v>
+        <v>36200</v>
       </c>
       <c r="Q11" t="n">
-        <v>87700</v>
+        <v>8920</v>
       </c>
       <c r="R11" t="n">
-        <v>2000</v>
+        <v>-7000</v>
       </c>
       <c r="S11" t="n">
-        <v>39000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>합병 반대 목소리와 함께 정유 및 배터리 업황 호조 기대. 주가 급락 및 상승 가능성 혼재.</t>
+          <t>이란의 미국과의 단계적 협상 합의 추진 소식에 유가 상승 기대감. 외인 매수세 유입.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['합병반대', '정유', '배터리']</t>
+          <t>['이란', '유가', '협상']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,77 +1476,77 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15090</v>
+        <v>141700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.93%</t>
+          <t>'+3.66%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-1.17</v>
+        <v>0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="F12" t="n">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="G12" t="n">
-        <v>372</v>
+        <v>338</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>15.81</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14660</v>
+        <v>136700</v>
       </c>
       <c r="K12" t="n">
-        <v>14980</v>
+        <v>139500</v>
       </c>
       <c r="L12" t="n">
-        <v>15460</v>
+        <v>144100</v>
       </c>
       <c r="M12" t="n">
-        <v>14330</v>
+        <v>138200</v>
       </c>
       <c r="N12" t="n">
-        <v>1.17</v>
+        <v>15.76</v>
       </c>
       <c r="O12" t="n">
-        <v>54550761575</v>
+        <v>114655154150</v>
       </c>
       <c r="P12" t="n">
-        <v>36200</v>
+        <v>164700</v>
       </c>
       <c r="Q12" t="n">
-        <v>8920</v>
+        <v>87700</v>
       </c>
       <c r="R12" t="n">
-        <v>-13000</v>
+        <v>-3000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>46000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>유가 상승 및 이란 관련 뉴스 언급. 4배 상승 기대감과 함께 외인 유입 및 장난질 가능성 언급. 3~5% 상승 메리트 부족 지적.</t>
+          <t>합병 반대 의견 다수. 정유주 슈퍼 사이클 및 배터리 사업 기대감 속에서도 주가 하락. 윗꼬리 현상 발생.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['유가', '이란', '외인']</t>
+          <t>['합병', '정유주', '배터리']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14500</v>
+        <v>14600</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.76%</t>
+          <t>'+3.47%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F13" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G13" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="H13" t="n">
         <v>10.75</v>
@@ -1622,7 +1622,7 @@
         <v>10.69</v>
       </c>
       <c r="O13" t="n">
-        <v>119763024730</v>
+        <v>121354202750</v>
       </c>
       <c r="P13" t="n">
         <v>23550</v>
@@ -1631,10 +1631,10 @@
         <v>5700</v>
       </c>
       <c r="R13" t="n">
-        <v>-116000</v>
+        <v>-120000</v>
       </c>
       <c r="S13" t="n">
-        <v>130000</v>
+        <v>135000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1667,83 +1667,83 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17590</v>
+        <v>10500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.27%</t>
+          <t>'+2.24%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-2.35</v>
+        <v>0.26</v>
       </c>
       <c r="E14" t="n">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="F14" t="n">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="G14" t="n">
-        <v>297</v>
+        <v>460</v>
       </c>
       <c r="H14" t="n">
-        <v>0.35</v>
+        <v>17.93</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>17200</v>
+        <v>10270</v>
       </c>
       <c r="K14" t="n">
-        <v>17220</v>
+        <v>11000</v>
       </c>
       <c r="L14" t="n">
-        <v>18390</v>
+        <v>11650</v>
       </c>
       <c r="M14" t="n">
-        <v>16600</v>
+        <v>10010</v>
       </c>
       <c r="N14" t="n">
-        <v>2.7</v>
+        <v>17.67</v>
       </c>
       <c r="O14" t="n">
-        <v>188179777275</v>
+        <v>339606823970</v>
       </c>
       <c r="P14" t="n">
-        <v>30550</v>
+        <v>22450</v>
       </c>
       <c r="Q14" t="n">
-        <v>6100</v>
+        <v>1760</v>
       </c>
       <c r="R14" t="n">
-        <v>-32000</v>
+        <v>181000</v>
       </c>
       <c r="S14" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 양자 보안주 폭등 및 세계 최초 타이틀 기반 신고가 경신.</t>
+          <t>아이온큐 급등 및 기타법인 매수세 유입으로 인한 기대감 고조. 트럼프 발언에 따른 AI 성장 기대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['양자 보안', '세계 최초', '신고가']</t>
+          <t>['아이온큐', 'AI', '기타법인']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10470</v>
+        <v>17550</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.95%</t>
+          <t>'+2.03%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.26</v>
+        <v>-2.35</v>
       </c>
       <c r="E15" t="n">
-        <v>179</v>
+        <v>213</v>
       </c>
       <c r="F15" t="n">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="G15" t="n">
-        <v>440</v>
+        <v>298</v>
       </c>
       <c r="H15" t="n">
-        <v>17.93</v>
+        <v>0.35</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>10270</v>
+        <v>17200</v>
       </c>
       <c r="K15" t="n">
-        <v>11000</v>
+        <v>17220</v>
       </c>
       <c r="L15" t="n">
-        <v>11650</v>
+        <v>18390</v>
       </c>
       <c r="M15" t="n">
-        <v>10010</v>
+        <v>16600</v>
       </c>
       <c r="N15" t="n">
-        <v>17.67</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
-        <v>337903780065</v>
+        <v>189967019625</v>
       </c>
       <c r="P15" t="n">
-        <v>22450</v>
+        <v>30550</v>
       </c>
       <c r="Q15" t="n">
-        <v>1760</v>
+        <v>6100</v>
       </c>
       <c r="R15" t="n">
-        <v>139000</v>
+        <v>-33000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>아이온큐 급등 및 트럼프 AI 정책 기대감 반영. 기타법인 매수세 유입. 광통신 테마와 연관성 언급.</t>
+          <t>미국 양자 보안주 폭등 및 세계 최초 타이틀 기반 신고가 경신.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['아이온큐', 'AI', '기타법인']</t>
+          <t>['양자 보안', '세계 최초', '신고가']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10110</v>
+        <v>18940</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.20%</t>
+          <t>'+0.96%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="E16" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="F16" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G16" t="n">
-        <v>144</v>
+        <v>434</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6</v>
+        <v>10.53</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,38 +1883,38 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>9990</v>
+        <v>18760</v>
       </c>
       <c r="K16" t="n">
-        <v>10110</v>
+        <v>18440</v>
       </c>
       <c r="L16" t="n">
-        <v>11390</v>
+        <v>19330</v>
       </c>
       <c r="M16" t="n">
-        <v>9980</v>
+        <v>18120</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6</v>
+        <v>10.55</v>
       </c>
       <c r="O16" t="n">
-        <v>156403663265</v>
+        <v>70535612210</v>
       </c>
       <c r="P16" t="n">
-        <v>15960</v>
+        <v>40350</v>
       </c>
       <c r="Q16" t="n">
-        <v>3500</v>
+        <v>3320</v>
       </c>
       <c r="R16" t="n">
-        <v>1000</v>
+        <v>23000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>부정적인 언급과 함께 주가 조작 의혹 제기. "저질약품", "최악" 등 부정적 표현 다수.</t>
+          <t>긍정적인 흐름과 대박 공시 기대감 형성. "대차해지" 독려 운동 활발.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['주가조작', '저질약품']</t>
+          <t>['대차해지', '공시', '흐름']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18910</v>
+        <v>10080</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.80%</t>
+          <t>'+0.90%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="F17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G17" t="n">
-        <v>404</v>
+        <v>157</v>
       </c>
       <c r="H17" t="n">
-        <v>10.53</v>
+        <v>0.6</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,38 +1975,38 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>18760</v>
+        <v>9990</v>
       </c>
       <c r="K17" t="n">
-        <v>18440</v>
+        <v>10110</v>
       </c>
       <c r="L17" t="n">
-        <v>19330</v>
+        <v>11390</v>
       </c>
       <c r="M17" t="n">
-        <v>18120</v>
+        <v>9980</v>
       </c>
       <c r="N17" t="n">
-        <v>10.55</v>
+        <v>0.6</v>
       </c>
       <c r="O17" t="n">
-        <v>68464701710</v>
+        <v>156866481315</v>
       </c>
       <c r="P17" t="n">
-        <v>40350</v>
+        <v>15960</v>
       </c>
       <c r="Q17" t="n">
-        <v>3320</v>
+        <v>3500</v>
       </c>
       <c r="R17" t="n">
-        <v>6000</v>
+        <v>-13000</v>
       </c>
       <c r="S17" t="n">
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>긍정적인 흐름과 대박 공시 기대감 형성. "대차해지" 독려 운동 활발.</t>
+          <t>부정적인 언급과 함께 주가 조작 의혹 제기. "저질약품", "최악" 등 부정적 표현 다수.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['대차해지', '공시', '흐름']</t>
+          <t>['주가조작', '저질약품']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
@@ -2039,18 +2039,18 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6930</v>
+        <v>6890</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.43%</t>
+          <t>'-0.14%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.97</v>
       </c>
       <c r="E18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F18" t="n">
         <v>37</v>
@@ -2082,7 +2082,7 @@
         <v>1.67</v>
       </c>
       <c r="O18" t="n">
-        <v>44862096045</v>
+        <v>45021619365</v>
       </c>
       <c r="P18" t="n">
         <v>10360</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>247000</v>
+        <v>246500</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-0.80%</t>
+          <t>'-1.00%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="G19" t="n">
-        <v>1515</v>
+        <v>1440</v>
       </c>
       <c r="H19" t="n">
         <v>46.57</v>
@@ -2168,13 +2168,13 @@
         <v>252000</v>
       </c>
       <c r="M19" t="n">
-        <v>247000</v>
+        <v>246000</v>
       </c>
       <c r="N19" t="n">
         <v>46.64</v>
       </c>
       <c r="O19" t="n">
-        <v>1953344501000</v>
+        <v>2057340748500</v>
       </c>
       <c r="P19" t="n">
         <v>374500</v>
@@ -2183,14 +2183,14 @@
         <v>75900</v>
       </c>
       <c r="R19" t="n">
-        <v>-252000</v>
+        <v>-368000</v>
       </c>
       <c r="S19" t="n">
-        <v>-480000</v>
+        <v>-472000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>시장 안정화 언급에도 불구하고 정치적 언급 및 게시판 불편함 토로. 금리 인상 선반영 및 특별배당 기대감 존재.</t>
+          <t>네이버 증권 게시판의 불편함 지적과 함께 정치 관련 논쟁이 혼재. 금리 인상 선반영 기대.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['금리인상', '특별배당', '정치']</t>
+          <t>['금리인상', '네이버증권', '정치']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1680000</v>
+        <v>1679000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-1.00%</t>
+          <t>'-1.06%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2237,10 +2237,10 @@
         <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G20" t="n">
-        <v>1628</v>
+        <v>1616</v>
       </c>
       <c r="H20" t="n">
         <v>50.27</v>
@@ -2260,13 +2260,13 @@
         <v>1729000</v>
       </c>
       <c r="M20" t="n">
-        <v>1680000</v>
+        <v>1671000</v>
       </c>
       <c r="N20" t="n">
         <v>50.47</v>
       </c>
       <c r="O20" t="n">
-        <v>3348848076500</v>
+        <v>3477053962500</v>
       </c>
       <c r="P20" t="n">
         <v>2987000</v>
@@ -2275,23 +2275,23 @@
         <v>325000</v>
       </c>
       <c r="R20" t="n">
-        <v>-232000</v>
+        <v>-297000</v>
       </c>
       <c r="S20" t="n">
-        <v>-67000</v>
+        <v>-84000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>AI 이슈 및 트럼프 발언에 따른 주가 변동성 관찰. 금리, 중국 메모리 등 다양한 이슈 언급. 투자 리스크보다 투자 안 하는 리스크가 크다는 의견.</t>
+          <t>AI 및 금리, 중국 메모리 등 다양한 이슈 속에서 주가 변동성 발생. 젠슨 황의 AI 위험론 부정 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['AI', '트럼프', '금리']</t>
+          <t>['AI', '금리', '젠슨황']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2326,13 +2326,13 @@
         <v>0.15</v>
       </c>
       <c r="E21" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F21" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G21" t="n">
-        <v>958</v>
+        <v>963</v>
       </c>
       <c r="H21" t="n">
         <v>7.2</v>
@@ -2358,7 +2358,7 @@
         <v>7.05</v>
       </c>
       <c r="O21" t="n">
-        <v>89525116250</v>
+        <v>91790491500</v>
       </c>
       <c r="P21" t="n">
         <v>426000</v>
@@ -2367,7 +2367,7 @@
         <v>89500</v>
       </c>
       <c r="R21" t="n">
-        <v>-128000</v>
+        <v>-120000</v>
       </c>
       <c r="S21" t="n">
         <v>1000</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8670</v>
+        <v>8650</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-2.03%</t>
+          <t>'-2.26%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="F22" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G22" t="n">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="H22" t="n">
         <v>27.16</v>
@@ -2444,13 +2444,13 @@
         <v>8840</v>
       </c>
       <c r="M22" t="n">
-        <v>8660</v>
+        <v>8630</v>
       </c>
       <c r="N22" t="n">
         <v>27.16</v>
       </c>
       <c r="O22" t="n">
-        <v>22645549770</v>
+        <v>24083348325</v>
       </c>
       <c r="P22" t="n">
         <v>17950</v>
@@ -2459,10 +2459,10 @@
         <v>8120</v>
       </c>
       <c r="R22" t="n">
-        <v>-351000</v>
+        <v>-565000</v>
       </c>
       <c r="S22" t="n">
-        <v>-2000</v>
+        <v>7000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2495,79 +2495,79 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14100</v>
+        <v>84600</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-2.69%</t>
+          <t>'-2.76%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="E23" t="n">
-        <v>113</v>
+        <v>252</v>
       </c>
       <c r="F23" t="n">
-        <v>63</v>
+        <v>139</v>
       </c>
       <c r="G23" t="n">
-        <v>499</v>
+        <v>904</v>
       </c>
       <c r="H23" t="n">
-        <v>1.8</v>
+        <v>23.45</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>14490</v>
+        <v>87000</v>
       </c>
       <c r="K23" t="n">
-        <v>14410</v>
+        <v>86200</v>
       </c>
       <c r="L23" t="n">
-        <v>14600</v>
+        <v>86800</v>
       </c>
       <c r="M23" t="n">
-        <v>13930</v>
+        <v>84200</v>
       </c>
       <c r="N23" t="n">
-        <v>1.88</v>
+        <v>23.56</v>
       </c>
       <c r="O23" t="n">
-        <v>59952711865</v>
+        <v>124780797900</v>
       </c>
       <c r="P23" t="n">
-        <v>31500</v>
+        <v>139200</v>
       </c>
       <c r="Q23" t="n">
-        <v>1272</v>
+        <v>57000</v>
       </c>
       <c r="R23" t="n">
-        <v>99000</v>
+        <v>-220000</v>
       </c>
       <c r="S23" t="n">
-        <v>-4000</v>
+        <v>-152000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>언론 홍보 효과 및 지지 구간 언급. AI, 광전자 관련 테마주로 긍정적 전망.</t>
+          <t>원전 사업 기대감과 함께 X에너지 급등. 두산에너빌리티 신용 매수 언급. 원전 ETF 추가 출시.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['언론홍보', '광통신', 'AI']</t>
+          <t>['원전', 'X에너지', 'ETF']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2575,91 +2575,91 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>84600</v>
+        <v>14070</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-2.76%</t>
+          <t>'-2.90%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="E24" t="n">
-        <v>235</v>
+        <v>116</v>
       </c>
       <c r="F24" t="n">
-        <v>132</v>
+        <v>64</v>
       </c>
       <c r="G24" t="n">
-        <v>873</v>
+        <v>506</v>
       </c>
       <c r="H24" t="n">
-        <v>23.45</v>
+        <v>1.8</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>87000</v>
+        <v>14490</v>
       </c>
       <c r="K24" t="n">
-        <v>86200</v>
+        <v>14410</v>
       </c>
       <c r="L24" t="n">
-        <v>86800</v>
+        <v>14600</v>
       </c>
       <c r="M24" t="n">
-        <v>84600</v>
+        <v>13930</v>
       </c>
       <c r="N24" t="n">
-        <v>23.56</v>
+        <v>1.88</v>
       </c>
       <c r="O24" t="n">
-        <v>118037342600</v>
+        <v>61587085205</v>
       </c>
       <c r="P24" t="n">
-        <v>139200</v>
+        <v>31500</v>
       </c>
       <c r="Q24" t="n">
-        <v>57000</v>
+        <v>1272</v>
       </c>
       <c r="R24" t="n">
-        <v>-153000</v>
+        <v>68000</v>
       </c>
       <c r="S24" t="n">
-        <v>-121000</v>
+        <v>-2000</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>두산에너빌리티는 원전 사업 관련 긍정적 언급과 함께 엑스에너지의 급등세를 기반으로 주가 상승을 기대하는 글들이 일부 있었다. 그러나 전날의 과도한 하락에 대한 언급도 존재한다.</t>
+          <t>언론 홍보 효과 및 지지 구간 언급. AI, 광전자 관련 테마주로 긍정적 전망.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['원전', '엑스에너지', '주가 상승']</t>
+          <t>['언론홍보', '광통신', 'AI']</t>
         </is>
       </c>
       <c r="X24" t="n">
@@ -2667,12 +2667,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4090</v>
+        <v>4085</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-5.43%</t>
+          <t>'-5.55%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>0.18</v>
       </c>
       <c r="E25" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F25" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G25" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H25" t="n">
         <v>0.77</v>
@@ -2726,7 +2726,7 @@
         <v>0.59</v>
       </c>
       <c r="O25" t="n">
-        <v>71532391711</v>
+        <v>72405175657</v>
       </c>
       <c r="P25" t="n">
         <v>8100</v>
@@ -2735,7 +2735,7 @@
         <v>592</v>
       </c>
       <c r="R25" t="n">
-        <v>-112000</v>
+        <v>-65000</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>20800</v>
+        <v>20700</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-5.88%</t>
+          <t>'-6.33%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.09</v>
       </c>
       <c r="E26" t="n">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="F26" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G26" t="n">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="H26" t="n">
         <v>28.9</v>
@@ -2818,7 +2818,7 @@
         <v>28.81</v>
       </c>
       <c r="O26" t="n">
-        <v>68101496425</v>
+        <v>69736948950</v>
       </c>
       <c r="P26" t="n">
         <v>35350</v>
@@ -2827,10 +2827,10 @@
         <v>18440</v>
       </c>
       <c r="R26" t="n">
-        <v>-1538000</v>
+        <v>-1833000</v>
       </c>
       <c r="S26" t="n">
-        <v>-65000</v>
+        <v>-60000</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/data/trending_integrated_20260915_14.xlsx
+++ b/data/trending_integrated_20260915_14.xlsx
@@ -578,13 +578,13 @@
         <v>1.34</v>
       </c>
       <c r="E2" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F2" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G2" t="n">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="H2" t="n">
         <v>1.34</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>119928138895</v>
+        <v>120914191375</v>
       </c>
       <c r="P2" t="n">
         <v>5100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>삼성과 4381억 계약 체결 확인. 광통신, 양자 관련 테마로 급등세. 주포 개입 가능성 언급.</t>
+          <t>삼성과 4381억 계약 체결 및 광통신, 양자 관련 테마 급등. 시원한 주가 상승세. 추가 상승 기대감 고조.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['삼성', '광통신', '양자']</t>
+          <t>['계약 체결', '광통신', '양자 테마']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -676,7 +676,7 @@
         <v>64</v>
       </c>
       <c r="G3" t="n">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="H3" t="n">
         <v>3.02</v>
@@ -702,7 +702,7 @@
         <v>3.56</v>
       </c>
       <c r="O3" t="n">
-        <v>65517183545</v>
+        <v>65636000845</v>
       </c>
       <c r="P3" t="n">
         <v>11370</v>
@@ -762,7 +762,7 @@
         <v>-0.31</v>
       </c>
       <c r="E4" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F4" t="n">
         <v>57</v>
@@ -794,7 +794,7 @@
         <v>2.99</v>
       </c>
       <c r="O4" t="n">
-        <v>48574572969</v>
+        <v>48597224099</v>
       </c>
       <c r="P4" t="n">
         <v>8980</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11270</v>
+        <v>11250</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+21.57%</t>
+          <t>'+21.36%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.06</v>
       </c>
       <c r="E5" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F5" t="n">
         <v>79</v>
       </c>
       <c r="G5" t="n">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H5" t="n">
         <v>1.19</v>
@@ -886,7 +886,7 @@
         <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>189488045760</v>
+        <v>191643668985</v>
       </c>
       <c r="P5" t="n">
         <v>25050</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>탈모 치료제 및 장기지속형 주사제 관련 특허 및 개발 기대감. 품절주 및 목표가 30만 언급.</t>
+          <t>탈모 치료제 관련 기대감 속 품절주 특성 부각. 신규 제형 및 특허 이슈로 인한 상승 가능성 언급. 목표가 상향 논의.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['탈모치료제', '장기지속형주사제', '특허']</t>
+          <t>['탈모 치료제', '품절주', '특허']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24750</v>
+        <v>24950</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+13.01%</t>
+          <t>'+13.93%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F6" t="n">
         <v>62</v>
       </c>
       <c r="G6" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H6" t="n">
         <v>4.9</v>
@@ -978,7 +978,7 @@
         <v>4.89</v>
       </c>
       <c r="O6" t="n">
-        <v>217245534050</v>
+        <v>219135581700</v>
       </c>
       <c r="P6" t="n">
         <v>50600</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34950</v>
+        <v>35050</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.91%</t>
+          <t>'+6.21%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.13</v>
       </c>
       <c r="E7" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G7" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="H7" t="n">
         <v>14.93</v>
@@ -1070,7 +1070,7 @@
         <v>15.06</v>
       </c>
       <c r="O7" t="n">
-        <v>53142455775</v>
+        <v>53646802425</v>
       </c>
       <c r="P7" t="n">
         <v>50400</v>
@@ -1115,123 +1115,123 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3585</v>
+        <v>50600</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.44%</t>
+          <t>'+5.86%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.12</v>
+        <v>-0.18</v>
       </c>
       <c r="E8" t="n">
-        <v>86</v>
+        <v>192</v>
       </c>
       <c r="F8" t="n">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="G8" t="n">
-        <v>211</v>
+        <v>608</v>
       </c>
       <c r="H8" t="n">
-        <v>0.83</v>
+        <v>13.97</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>3400</v>
+        <v>47800</v>
       </c>
       <c r="K8" t="n">
-        <v>3450</v>
+        <v>47300</v>
       </c>
       <c r="L8" t="n">
-        <v>4080</v>
+        <v>54600</v>
       </c>
       <c r="M8" t="n">
-        <v>3445</v>
+        <v>46400</v>
       </c>
       <c r="N8" t="n">
-        <v>0.71</v>
+        <v>14.15</v>
       </c>
       <c r="O8" t="n">
-        <v>150601114122</v>
+        <v>91201494775</v>
       </c>
       <c r="P8" t="n">
-        <v>4335</v>
+        <v>108900</v>
       </c>
       <c r="Q8" t="n">
-        <v>1246</v>
+        <v>18230</v>
       </c>
       <c r="R8" t="n">
-        <v>-32000</v>
+        <v>70000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>65000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>긍정적인 상승 파동 기대감 및 세력 움직임 언급. "날아간다", "대장" 등 긍정적 표현.</t>
+          <t>연이은 수주 공시에도 불구하고 주가 상승 미미. 하이퍼스케일러 수주 및 송전망 건설 관련 논의. 공매도 세력에 대한 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['상승파동', '대장', '세력']</t>
+          <t>['수주 공시', '하이퍼스케일러', '송전망']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31700</v>
+        <v>3595</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.45%</t>
+          <t>'+5.74%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.05</v>
+        <v>0.12</v>
       </c>
       <c r="E9" t="n">
-        <v>176</v>
+        <v>86</v>
       </c>
       <c r="F9" t="n">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="G9" t="n">
-        <v>890</v>
+        <v>211</v>
       </c>
       <c r="H9" t="n">
-        <v>17.5</v>
+        <v>0.83</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,139 +1239,139 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>30350</v>
+        <v>3400</v>
       </c>
       <c r="K9" t="n">
-        <v>30250</v>
+        <v>3450</v>
       </c>
       <c r="L9" t="n">
-        <v>32300</v>
+        <v>4080</v>
       </c>
       <c r="M9" t="n">
-        <v>30250</v>
+        <v>3445</v>
       </c>
       <c r="N9" t="n">
-        <v>17.55</v>
+        <v>0.71</v>
       </c>
       <c r="O9" t="n">
-        <v>14608817350</v>
+        <v>151051743547</v>
       </c>
       <c r="P9" t="n">
-        <v>69200</v>
+        <v>4335</v>
       </c>
       <c r="Q9" t="n">
-        <v>24150</v>
+        <v>1246</v>
       </c>
       <c r="R9" t="n">
-        <v>82000</v>
+        <v>-32000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>담관암 FDA 승인 관련 기대와 CRL 공시로 인한 실망감 공존. 기관 외인 매도세 관찰되며, 이유 없는 급락에 대한 분석 요구.</t>
+          <t>긍정적인 상승 파동 기대감 및 세력 움직임 언급. "날아간다", "대장" 등 긍정적 표현.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['담관암', 'FDA승인', 'CRL']</t>
+          <t>['상승파동', '대장', '세력']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49850</v>
+        <v>31950</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.29%</t>
+          <t>'+5.27%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.18</v>
+        <v>-0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="F10" t="n">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="G10" t="n">
-        <v>601</v>
+        <v>935</v>
       </c>
       <c r="H10" t="n">
-        <v>13.97</v>
+        <v>17.5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>47800</v>
+        <v>30350</v>
       </c>
       <c r="K10" t="n">
-        <v>47300</v>
+        <v>30250</v>
       </c>
       <c r="L10" t="n">
-        <v>54600</v>
+        <v>32300</v>
       </c>
       <c r="M10" t="n">
-        <v>46400</v>
+        <v>30250</v>
       </c>
       <c r="N10" t="n">
-        <v>14.15</v>
+        <v>17.55</v>
       </c>
       <c r="O10" t="n">
-        <v>89665845875</v>
+        <v>14935102275</v>
       </c>
       <c r="P10" t="n">
-        <v>108900</v>
+        <v>69200</v>
       </c>
       <c r="Q10" t="n">
-        <v>18230</v>
+        <v>24150</v>
       </c>
       <c r="R10" t="n">
-        <v>70000</v>
+        <v>82000</v>
       </c>
       <c r="S10" t="n">
-        <v>65000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>연이은 수주 공시에도 주가 부진, 유상증자 변수 및 공매도 관련 논의.</t>
+          <t>담관암 치료제 FDA 승인 기대감과 주가 하락세 공존. 기관 및 외인 매도세에 대한 우려. 탐욕과 기다림에 대한 논의.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['수주', '공시', '유상증자']</t>
+          <t>['담관암', 'FDA 승인', '주가 하락']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15260</v>
+        <v>142200</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+4.09%</t>
+          <t>'+4.02%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-1.17</v>
+        <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>187</v>
+        <v>142</v>
       </c>
       <c r="F11" t="n">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="G11" t="n">
-        <v>386</v>
+        <v>336</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>15.81</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>14660</v>
+        <v>136700</v>
       </c>
       <c r="K11" t="n">
-        <v>14980</v>
+        <v>139500</v>
       </c>
       <c r="L11" t="n">
-        <v>15460</v>
+        <v>144100</v>
       </c>
       <c r="M11" t="n">
-        <v>14330</v>
+        <v>138200</v>
       </c>
       <c r="N11" t="n">
-        <v>1.17</v>
+        <v>15.76</v>
       </c>
       <c r="O11" t="n">
-        <v>60506493015</v>
+        <v>116682301500</v>
       </c>
       <c r="P11" t="n">
-        <v>36200</v>
+        <v>164700</v>
       </c>
       <c r="Q11" t="n">
-        <v>8920</v>
+        <v>87700</v>
       </c>
       <c r="R11" t="n">
-        <v>-7000</v>
+        <v>-3000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>46000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>이란의 미국과의 단계적 협상 합의 추진 소식에 유가 상승 기대감. 외인 매수세 유입.</t>
+          <t>합병 반대 의견 다수. 정유주 슈퍼 사이클 및 배터리 사업 기대감 속에서도 주가 하락. 윗꼬리 현상 발생.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['이란', '유가', '협상']</t>
+          <t>['합병', '정유주', '배터리']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>141700</v>
+        <v>14660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.66%</t>
+          <t>'+3.90%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>143</v>
+        <v>62</v>
       </c>
       <c r="F12" t="n">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="G12" t="n">
-        <v>338</v>
+        <v>200</v>
       </c>
       <c r="H12" t="n">
-        <v>15.81</v>
+        <v>10.75</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,47 +1515,47 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>136700</v>
+        <v>14110</v>
       </c>
       <c r="K12" t="n">
-        <v>139500</v>
+        <v>14110</v>
       </c>
       <c r="L12" t="n">
-        <v>144100</v>
+        <v>15250</v>
       </c>
       <c r="M12" t="n">
-        <v>138200</v>
+        <v>13400</v>
       </c>
       <c r="N12" t="n">
-        <v>15.76</v>
+        <v>10.69</v>
       </c>
       <c r="O12" t="n">
-        <v>114655154150</v>
+        <v>122434893490</v>
       </c>
       <c r="P12" t="n">
-        <v>164700</v>
+        <v>23550</v>
       </c>
       <c r="Q12" t="n">
-        <v>87700</v>
+        <v>5700</v>
       </c>
       <c r="R12" t="n">
-        <v>-3000</v>
+        <v>-120000</v>
       </c>
       <c r="S12" t="n">
-        <v>46000</v>
+        <v>137000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>합병 반대 의견 다수. 정유주 슈퍼 사이클 및 배터리 사업 기대감 속에서도 주가 하락. 윗꼬리 현상 발생.</t>
+          <t>거래량 증가와 함께 15000원 돌파 시도, 주포 움직임에 대한 기대와 우려 혼재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['합병', '정유주', '배터리']</t>
+          <t>['주포', '거래량', '15000원']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1563,43 +1563,43 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>093370</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14600</v>
+        <v>10600</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.47%</t>
+          <t>'+3.21%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.06</v>
+        <v>0.26</v>
       </c>
       <c r="E13" t="n">
-        <v>60</v>
+        <v>186</v>
       </c>
       <c r="F13" t="n">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="G13" t="n">
-        <v>199</v>
+        <v>469</v>
       </c>
       <c r="H13" t="n">
-        <v>10.75</v>
+        <v>17.93</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,143 +1607,143 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>14110</v>
+        <v>10270</v>
       </c>
       <c r="K13" t="n">
-        <v>14110</v>
+        <v>11000</v>
       </c>
       <c r="L13" t="n">
-        <v>15250</v>
+        <v>11650</v>
       </c>
       <c r="M13" t="n">
-        <v>13400</v>
+        <v>10010</v>
       </c>
       <c r="N13" t="n">
-        <v>10.69</v>
+        <v>17.67</v>
       </c>
       <c r="O13" t="n">
-        <v>121354202750</v>
+        <v>342363030420</v>
       </c>
       <c r="P13" t="n">
-        <v>23550</v>
+        <v>22450</v>
       </c>
       <c r="Q13" t="n">
-        <v>5700</v>
+        <v>1760</v>
       </c>
       <c r="R13" t="n">
-        <v>-120000</v>
+        <v>181000</v>
       </c>
       <c r="S13" t="n">
-        <v>135000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>거래량 증가와 함께 15000원 돌파 시도, 주포 움직임에 대한 기대와 우려 혼재.</t>
+          <t>아이온큐 급등 및 기타법인 매수세 유입으로 인한 기대감 고조. 트럼프 발언에 따른 AI 성장 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['주포', '거래량', '15000원']</t>
+          <t>['아이온큐', 'AI', '기타법인']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10500</v>
+        <v>15110</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.24%</t>
+          <t>'+3.07%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.26</v>
+        <v>-1.17</v>
       </c>
       <c r="E14" t="n">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="F14" t="n">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="G14" t="n">
-        <v>460</v>
+        <v>406</v>
       </c>
       <c r="H14" t="n">
-        <v>17.93</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>10270</v>
+        <v>14660</v>
       </c>
       <c r="K14" t="n">
-        <v>11000</v>
+        <v>14980</v>
       </c>
       <c r="L14" t="n">
-        <v>11650</v>
+        <v>15460</v>
       </c>
       <c r="M14" t="n">
-        <v>10010</v>
+        <v>14330</v>
       </c>
       <c r="N14" t="n">
-        <v>17.67</v>
+        <v>1.17</v>
       </c>
       <c r="O14" t="n">
-        <v>339606823970</v>
+        <v>63018057620</v>
       </c>
       <c r="P14" t="n">
-        <v>22450</v>
+        <v>36200</v>
       </c>
       <c r="Q14" t="n">
-        <v>1760</v>
+        <v>8920</v>
       </c>
       <c r="R14" t="n">
-        <v>181000</v>
+        <v>-7000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>아이온큐 급등 및 기타법인 매수세 유입으로 인한 기대감 고조. 트럼프 발언에 따른 AI 성장 기대.</t>
+          <t>이란 관련 지정학적 이슈로 인한 유가 상승 기대감. 단계적 협상 합의 추진 소식에 주목. 유가 변동에 따른 주가 등락 예상.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['아이온큐', 'AI', '기타법인']</t>
+          <t>['이란', '유가', '지정학적']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,191 +1752,191 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17550</v>
+        <v>19150</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.03%</t>
+          <t>'+2.08%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-2.35</v>
+        <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>213</v>
+        <v>89</v>
       </c>
       <c r="F15" t="n">
-        <v>110</v>
+        <v>51</v>
       </c>
       <c r="G15" t="n">
-        <v>298</v>
+        <v>439</v>
       </c>
       <c r="H15" t="n">
-        <v>0.35</v>
+        <v>10.53</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>17200</v>
+        <v>18760</v>
       </c>
       <c r="K15" t="n">
-        <v>17220</v>
+        <v>18440</v>
       </c>
       <c r="L15" t="n">
-        <v>18390</v>
+        <v>19330</v>
       </c>
       <c r="M15" t="n">
-        <v>16600</v>
+        <v>18120</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>10.55</v>
       </c>
       <c r="O15" t="n">
-        <v>189967019625</v>
+        <v>72378360565</v>
       </c>
       <c r="P15" t="n">
-        <v>30550</v>
+        <v>40350</v>
       </c>
       <c r="Q15" t="n">
-        <v>6100</v>
+        <v>3320</v>
       </c>
       <c r="R15" t="n">
-        <v>-33000</v>
+        <v>23000</v>
       </c>
       <c r="S15" t="n">
-        <v>2000</v>
+        <v>29000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 양자 보안주 폭등 및 세계 최초 타이틀 기반 신고가 경신.</t>
+          <t>긍정적인 흐름과 대박 공시 기대감 형성. "대차해지" 독려 운동 활발.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['양자 보안', '세계 최초', '신고가']</t>
+          <t>['대차해지', '공시', '흐름']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18940</v>
+        <v>17420</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.96%</t>
+          <t>'+1.28%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.02</v>
+        <v>-2.35</v>
       </c>
       <c r="E16" t="n">
-        <v>89</v>
+        <v>218</v>
       </c>
       <c r="F16" t="n">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="G16" t="n">
-        <v>434</v>
+        <v>313</v>
       </c>
       <c r="H16" t="n">
-        <v>10.53</v>
+        <v>0.35</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>18760</v>
+        <v>17200</v>
       </c>
       <c r="K16" t="n">
-        <v>18440</v>
+        <v>17220</v>
       </c>
       <c r="L16" t="n">
-        <v>19330</v>
+        <v>18390</v>
       </c>
       <c r="M16" t="n">
-        <v>18120</v>
+        <v>16600</v>
       </c>
       <c r="N16" t="n">
-        <v>10.55</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
-        <v>70535612210</v>
+        <v>191880630570</v>
       </c>
       <c r="P16" t="n">
-        <v>40350</v>
+        <v>30550</v>
       </c>
       <c r="Q16" t="n">
-        <v>3320</v>
+        <v>6100</v>
       </c>
       <c r="R16" t="n">
-        <v>23000</v>
+        <v>-33000</v>
       </c>
       <c r="S16" t="n">
-        <v>35000</v>
+        <v>2000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>긍정적인 흐름과 대박 공시 기대감 형성. "대차해지" 독려 운동 활발.</t>
+          <t>미국 양자 보안주 급등에 따른 동반 상승 기대. 세계 최초 타이틀 강조. 주포의 움직임에 대한 관찰 및 주가 흐름에 대한 아쉬움 표출.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['대차해지', '공시', '흐름']</t>
+          <t>['양자 보안', '신고가', '주포']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10080</v>
+        <v>10030</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.90%</t>
+          <t>'+0.40%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F17" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G17" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H17" t="n">
         <v>0.6</v>
@@ -1990,7 +1990,7 @@
         <v>0.6</v>
       </c>
       <c r="O17" t="n">
-        <v>156866481315</v>
+        <v>157134542370</v>
       </c>
       <c r="P17" t="n">
         <v>15960</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6890</v>
+        <v>6905</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-0.14%</t>
+          <t>'+0.07%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.97</v>
       </c>
       <c r="E18" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F18" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G18" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H18" t="n">
         <v>0.7</v>
@@ -2082,7 +2082,7 @@
         <v>1.67</v>
       </c>
       <c r="O18" t="n">
-        <v>45021619365</v>
+        <v>45188181180</v>
       </c>
       <c r="P18" t="n">
         <v>10360</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>246500</v>
+        <v>248000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-1.00%</t>
+          <t>'-0.40%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="G19" t="n">
-        <v>1440</v>
+        <v>1435</v>
       </c>
       <c r="H19" t="n">
         <v>46.57</v>
@@ -2174,7 +2174,7 @@
         <v>46.64</v>
       </c>
       <c r="O19" t="n">
-        <v>2057340748500</v>
+        <v>2153543095000</v>
       </c>
       <c r="P19" t="n">
         <v>374500</v>
@@ -2186,7 +2186,7 @@
         <v>-368000</v>
       </c>
       <c r="S19" t="n">
-        <v>-472000</v>
+        <v>-565000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1679000</v>
+        <v>1683000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-1.06%</t>
+          <t>'-0.82%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2237,10 +2237,10 @@
         <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G20" t="n">
-        <v>1616</v>
+        <v>1590</v>
       </c>
       <c r="H20" t="n">
         <v>50.27</v>
@@ -2266,7 +2266,7 @@
         <v>50.47</v>
       </c>
       <c r="O20" t="n">
-        <v>3477053962500</v>
+        <v>3601551227000</v>
       </c>
       <c r="P20" t="n">
         <v>2987000</v>
@@ -2278,20 +2278,20 @@
         <v>-297000</v>
       </c>
       <c r="S20" t="n">
-        <v>-84000</v>
+        <v>-104000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>AI 및 금리, 중국 메모리 등 다양한 이슈 속에서 주가 변동성 발생. 젠슨 황의 AI 위험론 부정 언급.</t>
+          <t>AI 및 금리 이슈로 인한 변동성 확대. 단기적인 주가 등락에도 불구하고 뚜렷한 방향성 부재. 투자자들의 피로감 누적.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['AI', '금리', '젠슨황']</t>
+          <t>['AI', '금리', '변동성']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2311,31 +2311,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>222000</v>
+        <v>86200</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-1.33%</t>
+          <t>'-0.92%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.15</v>
+        <v>-0.11</v>
       </c>
       <c r="E21" t="n">
-        <v>176</v>
+        <v>262</v>
       </c>
       <c r="F21" t="n">
-        <v>86</v>
+        <v>140</v>
       </c>
       <c r="G21" t="n">
-        <v>963</v>
+        <v>924</v>
       </c>
       <c r="H21" t="n">
-        <v>7.2</v>
+        <v>23.45</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,38 +2343,38 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>225000</v>
+        <v>87000</v>
       </c>
       <c r="K21" t="n">
-        <v>228500</v>
+        <v>86200</v>
       </c>
       <c r="L21" t="n">
-        <v>229000</v>
+        <v>86800</v>
       </c>
       <c r="M21" t="n">
-        <v>219500</v>
+        <v>84200</v>
       </c>
       <c r="N21" t="n">
-        <v>7.05</v>
+        <v>23.56</v>
       </c>
       <c r="O21" t="n">
-        <v>91790491500</v>
+        <v>135167024150</v>
       </c>
       <c r="P21" t="n">
-        <v>426000</v>
+        <v>139200</v>
       </c>
       <c r="Q21" t="n">
-        <v>89500</v>
+        <v>57000</v>
       </c>
       <c r="R21" t="n">
-        <v>-120000</v>
+        <v>-220000</v>
       </c>
       <c r="S21" t="n">
-        <v>1000</v>
+        <v>-152000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>머스크의 테라팹에 패키징 장비 공급 단독 보도. 공매도 세력과의 갈등 양상.</t>
+          <t>원전 사업 기대감과 함께 X에너지 급등. 두산에너빌리티 신용 매수 언급. 원전 ETF 추가 출시.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,11 +2383,11 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['패키징', '테라팹', '공매도']</t>
+          <t>['원전', 'X에너지', 'ETF']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8650</v>
+        <v>222500</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-2.26%</t>
+          <t>'-1.11%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E22" t="n">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="F22" t="n">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="G22" t="n">
-        <v>463</v>
+        <v>969</v>
       </c>
       <c r="H22" t="n">
-        <v>27.16</v>
+        <v>7.2</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,38 +2435,38 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>8850</v>
+        <v>225000</v>
       </c>
       <c r="K22" t="n">
-        <v>8750</v>
+        <v>228500</v>
       </c>
       <c r="L22" t="n">
-        <v>8840</v>
+        <v>229000</v>
       </c>
       <c r="M22" t="n">
-        <v>8630</v>
+        <v>219500</v>
       </c>
       <c r="N22" t="n">
-        <v>27.16</v>
+        <v>7.05</v>
       </c>
       <c r="O22" t="n">
-        <v>24083348325</v>
+        <v>94365827500</v>
       </c>
       <c r="P22" t="n">
-        <v>17950</v>
+        <v>426000</v>
       </c>
       <c r="Q22" t="n">
-        <v>8120</v>
+        <v>89500</v>
       </c>
       <c r="R22" t="n">
-        <v>-565000</v>
+        <v>-120000</v>
       </c>
       <c r="S22" t="n">
-        <v>7000</v>
+        <v>1000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>목표주가 상향 조정에도 불구하고 주가 부진 지속. 연기금 순매수세 관찰되나, 컨센서스 하회 및 실적 부진에 대한 우려 제기.</t>
+          <t>머스크의 테라팹에 패키징 장비 공급 단독 보도. 공매도 세력과의 갈등 양상.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,11 +2475,11 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['목표주가', '실적부진', '연기금']</t>
+          <t>['패키징', '테라팹', '공매도']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,38 +2488,38 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>84600</v>
+        <v>8650</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-2.76%</t>
+          <t>'-2.26%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>252</v>
+        <v>142</v>
       </c>
       <c r="F23" t="n">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="G23" t="n">
-        <v>904</v>
+        <v>474</v>
       </c>
       <c r="H23" t="n">
-        <v>23.45</v>
+        <v>27.16</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,38 +2527,38 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>87000</v>
+        <v>8850</v>
       </c>
       <c r="K23" t="n">
-        <v>86200</v>
+        <v>8750</v>
       </c>
       <c r="L23" t="n">
-        <v>86800</v>
+        <v>8840</v>
       </c>
       <c r="M23" t="n">
-        <v>84200</v>
+        <v>8630</v>
       </c>
       <c r="N23" t="n">
-        <v>23.56</v>
+        <v>27.16</v>
       </c>
       <c r="O23" t="n">
-        <v>124780797900</v>
+        <v>24528452800</v>
       </c>
       <c r="P23" t="n">
-        <v>139200</v>
+        <v>17950</v>
       </c>
       <c r="Q23" t="n">
-        <v>57000</v>
+        <v>8120</v>
       </c>
       <c r="R23" t="n">
-        <v>-220000</v>
+        <v>-565000</v>
       </c>
       <c r="S23" t="n">
-        <v>-152000</v>
+        <v>7000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>원전 사업 기대감과 함께 X에너지 급등. 두산에너빌리티 신용 매수 언급. 원전 ETF 추가 출시.</t>
+          <t>목표주가 상향 조정에도 불구하고 주가 부진 지속. 연기금 순매수세 관찰되나, 컨센서스 하회 및 실적 부진에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,11 +2567,11 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['원전', 'X에너지', 'ETF']</t>
+          <t>['목표주가', '실적부진', '연기금']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14070</v>
+        <v>14120</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-2.90%</t>
+          <t>'-2.55%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.08</v>
       </c>
       <c r="E24" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F24" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G24" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="H24" t="n">
         <v>1.8</v>
@@ -2634,7 +2634,7 @@
         <v>1.88</v>
       </c>
       <c r="O24" t="n">
-        <v>61587085205</v>
+        <v>62302109700</v>
       </c>
       <c r="P24" t="n">
         <v>31500</v>
@@ -2683,11 +2683,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4085</v>
+        <v>4115</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-5.55%</t>
+          <t>'-4.86%</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -2726,7 +2726,7 @@
         <v>0.59</v>
       </c>
       <c r="O25" t="n">
-        <v>72405175657</v>
+        <v>73165416066</v>
       </c>
       <c r="P25" t="n">
         <v>8100</v>
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>20700</v>
+        <v>20750</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-6.33%</t>
+          <t>'-6.11%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.09</v>
       </c>
       <c r="E26" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F26" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G26" t="n">
-        <v>540</v>
+        <v>559</v>
       </c>
       <c r="H26" t="n">
         <v>28.9</v>
@@ -2812,13 +2812,13 @@
         <v>21850</v>
       </c>
       <c r="M26" t="n">
-        <v>20700</v>
+        <v>20650</v>
       </c>
       <c r="N26" t="n">
         <v>28.81</v>
       </c>
       <c r="O26" t="n">
-        <v>69736948950</v>
+        <v>71008489575</v>
       </c>
       <c r="P26" t="n">
         <v>35350</v>
@@ -2830,20 +2830,20 @@
         <v>-1833000</v>
       </c>
       <c r="S26" t="n">
-        <v>-60000</v>
+        <v>-56000</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>12억 달러 수주 공시에도 주가 하락. 시장은 수주를 악재로 인식하며, 공매도 및 기타 법인 매도세 관찰됨. 자사주 소각 등 주가 부양책 요구.</t>
+          <t>12억 달러 수주 공시에도 불구하고 주가 하락. 시장은 수주를 악재로 인식하는 분위기. 개인 투자자들의 불만 표출.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['수주공시', '주가하락', '공매도']</t>
+          <t>['수주 공시', '조선업', '주가 하락']</t>
         </is>
       </c>
       <c r="X26" t="n">

--- a/data/trending_integrated_20260915_14.xlsx
+++ b/data/trending_integrated_20260915_14.xlsx
@@ -578,13 +578,13 @@
         <v>1.34</v>
       </c>
       <c r="E2" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="F2" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G2" t="n">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="H2" t="n">
         <v>1.34</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>120914191375</v>
+        <v>125215835600</v>
       </c>
       <c r="P2" t="n">
         <v>5100</v>
@@ -670,13 +670,13 @@
         <v>-0.54</v>
       </c>
       <c r="E3" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="H3" t="n">
         <v>3.02</v>
@@ -702,7 +702,7 @@
         <v>3.56</v>
       </c>
       <c r="O3" t="n">
-        <v>65636000845</v>
+        <v>65779010685</v>
       </c>
       <c r="P3" t="n">
         <v>11370</v>
@@ -762,13 +762,13 @@
         <v>-0.31</v>
       </c>
       <c r="E4" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G4" t="n">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="H4" t="n">
         <v>2.68</v>
@@ -794,7 +794,7 @@
         <v>2.99</v>
       </c>
       <c r="O4" t="n">
-        <v>48597224099</v>
+        <v>48631668879</v>
       </c>
       <c r="P4" t="n">
         <v>8980</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11250</v>
+        <v>11290</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+21.36%</t>
+          <t>'+21.79%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.06</v>
       </c>
       <c r="E5" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F5" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G5" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H5" t="n">
         <v>1.19</v>
@@ -886,7 +886,7 @@
         <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>191643668985</v>
+        <v>193383401310</v>
       </c>
       <c r="P5" t="n">
         <v>25050</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>탈모 치료제 관련 기대감 속 품절주 특성 부각. 신규 제형 및 특허 이슈로 인한 상승 가능성 언급. 목표가 상향 논의.</t>
+          <t>탈모 치료제 관련 세계 최초 타이틀 및 장기 지속형 주사제 개발로 기대감이 형성됨. 노보노디스크와의 L/O 및 팹트론 개방 소식이 전해졌으며, 유통 물량 대비 높은 시가총액으로 상승 가능성이 언급됨.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['탈모 치료제', '품절주', '특허']</t>
+          <t>['탈모치료제', '지속형주사제', 'L/O']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24950</v>
+        <v>25050</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+13.93%</t>
+          <t>'+14.38%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G6" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H6" t="n">
         <v>4.9</v>
@@ -978,7 +978,7 @@
         <v>4.89</v>
       </c>
       <c r="O6" t="n">
-        <v>219135581700</v>
+        <v>220249623775</v>
       </c>
       <c r="P6" t="n">
         <v>50600</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>현대제철</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>35050</v>
+        <v>50800</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.21%</t>
+          <t>'+6.28%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.13</v>
+        <v>-0.18</v>
       </c>
       <c r="E7" t="n">
-        <v>86</v>
+        <v>192</v>
       </c>
       <c r="F7" t="n">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="G7" t="n">
-        <v>311</v>
+        <v>610</v>
       </c>
       <c r="H7" t="n">
-        <v>14.93</v>
+        <v>13.97</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>33000</v>
+        <v>47800</v>
       </c>
       <c r="K7" t="n">
-        <v>32750</v>
+        <v>47300</v>
       </c>
       <c r="L7" t="n">
-        <v>37200</v>
+        <v>54600</v>
       </c>
       <c r="M7" t="n">
-        <v>32750</v>
+        <v>46400</v>
       </c>
       <c r="N7" t="n">
-        <v>15.06</v>
+        <v>14.15</v>
       </c>
       <c r="O7" t="n">
-        <v>53646802425</v>
+        <v>92109780925</v>
       </c>
       <c r="P7" t="n">
-        <v>50400</v>
+        <v>108900</v>
       </c>
       <c r="Q7" t="n">
-        <v>23650</v>
+        <v>18230</v>
       </c>
       <c r="R7" t="n">
-        <v>349000</v>
+        <v>70000</v>
       </c>
       <c r="S7" t="n">
-        <v>109000</v>
+        <v>65000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>PBR 0.22, 0.07 등 저평가 지표와 한국거래소의 저PBR 기업 딱지 관련 뉴스를 바탕으로 상승 기대감이 형성됨. 120일선 돌파 등 기술적 지표도 언급됨.</t>
+          <t>연이은 수주 공시에도 불구하고 주가 상승 미미. 하이퍼스케일러 수주 및 송전망 건설 관련 논의. 공매도 세력에 대한 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['PBR', '저평가', '정배열']</t>
+          <t>['수주 공시', '하이퍼스케일러', '송전망']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,43 +1103,43 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>004020</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>현대제철</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50600</v>
+        <v>35050</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.86%</t>
+          <t>'+6.21%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.18</v>
+        <v>-0.13</v>
       </c>
       <c r="E8" t="n">
-        <v>192</v>
+        <v>87</v>
       </c>
       <c r="F8" t="n">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="G8" t="n">
-        <v>608</v>
+        <v>320</v>
       </c>
       <c r="H8" t="n">
-        <v>13.97</v>
+        <v>14.93</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,47 +1147,47 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>47800</v>
+        <v>33000</v>
       </c>
       <c r="K8" t="n">
-        <v>47300</v>
+        <v>32750</v>
       </c>
       <c r="L8" t="n">
-        <v>54600</v>
+        <v>37200</v>
       </c>
       <c r="M8" t="n">
-        <v>46400</v>
+        <v>32750</v>
       </c>
       <c r="N8" t="n">
-        <v>14.15</v>
+        <v>15.06</v>
       </c>
       <c r="O8" t="n">
-        <v>91201494775</v>
+        <v>54018597475</v>
       </c>
       <c r="P8" t="n">
-        <v>108900</v>
+        <v>50400</v>
       </c>
       <c r="Q8" t="n">
-        <v>18230</v>
+        <v>23650</v>
       </c>
       <c r="R8" t="n">
-        <v>70000</v>
+        <v>349000</v>
       </c>
       <c r="S8" t="n">
-        <v>65000</v>
+        <v>109000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>연이은 수주 공시에도 불구하고 주가 상승 미미. 하이퍼스케일러 수주 및 송전망 건설 관련 논의. 공매도 세력에 대한 언급.</t>
+          <t>PBR 0.22, 0.07 등 저평가 지표와 한국거래소의 저PBR 기업 딱지 관련 뉴스를 바탕으로 상승 기대감이 형성됨. 120일선 돌파 등 기술적 지표도 언급됨.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['수주 공시', '하이퍼스케일러', '송전망']</t>
+          <t>['PBR', '저평가', '정배열']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,43 +1195,43 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>004020</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3595</v>
+        <v>32150</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.74%</t>
+          <t>'+5.93%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.12</v>
+        <v>-0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>86</v>
+        <v>182</v>
       </c>
       <c r="F9" t="n">
-        <v>48</v>
+        <v>115</v>
       </c>
       <c r="G9" t="n">
-        <v>211</v>
+        <v>943</v>
       </c>
       <c r="H9" t="n">
-        <v>0.83</v>
+        <v>17.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,91 +1239,91 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>3400</v>
+        <v>30350</v>
       </c>
       <c r="K9" t="n">
-        <v>3450</v>
+        <v>30250</v>
       </c>
       <c r="L9" t="n">
-        <v>4080</v>
+        <v>32300</v>
       </c>
       <c r="M9" t="n">
-        <v>3445</v>
+        <v>30250</v>
       </c>
       <c r="N9" t="n">
-        <v>0.71</v>
+        <v>17.55</v>
       </c>
       <c r="O9" t="n">
-        <v>151051743547</v>
+        <v>15567304125</v>
       </c>
       <c r="P9" t="n">
-        <v>4335</v>
+        <v>69200</v>
       </c>
       <c r="Q9" t="n">
-        <v>1246</v>
+        <v>24150</v>
       </c>
       <c r="R9" t="n">
-        <v>-32000</v>
+        <v>82000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>긍정적인 상승 파동 기대감 및 세력 움직임 언급. "날아간다", "대장" 등 긍정적 표현.</t>
+          <t>담관암 치료제 FDA 승인 기대감과 주가 하락세 공존. 기관 및 외인 매도세에 대한 우려. 탐욕과 기다림에 대한 논의.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['상승파동', '대장', '세력']</t>
+          <t>['담관암', 'FDA 승인', '주가 하락']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31950</v>
+        <v>3575</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+5.27%</t>
+          <t>'+5.15%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.05</v>
+        <v>0.12</v>
       </c>
       <c r="E10" t="n">
-        <v>178</v>
+        <v>90</v>
       </c>
       <c r="F10" t="n">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c r="G10" t="n">
-        <v>935</v>
+        <v>215</v>
       </c>
       <c r="H10" t="n">
-        <v>17.5</v>
+        <v>0.83</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,60 +1331,60 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>30350</v>
+        <v>3400</v>
       </c>
       <c r="K10" t="n">
-        <v>30250</v>
+        <v>3450</v>
       </c>
       <c r="L10" t="n">
-        <v>32300</v>
+        <v>4080</v>
       </c>
       <c r="M10" t="n">
-        <v>30250</v>
+        <v>3445</v>
       </c>
       <c r="N10" t="n">
-        <v>17.55</v>
+        <v>0.71</v>
       </c>
       <c r="O10" t="n">
-        <v>14935102275</v>
+        <v>151735871672</v>
       </c>
       <c r="P10" t="n">
-        <v>69200</v>
+        <v>4335</v>
       </c>
       <c r="Q10" t="n">
-        <v>24150</v>
+        <v>1246</v>
       </c>
       <c r="R10" t="n">
-        <v>82000</v>
+        <v>-32000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>담관암 치료제 FDA 승인 기대감과 주가 하락세 공존. 기관 및 외인 매도세에 대한 우려. 탐욕과 기다림에 대한 논의.</t>
+          <t>긍정적인 상승 파동 기대감 및 세력 움직임 언급. "날아간다", "대장" 등 긍정적 표현.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['담관암', 'FDA 승인', '주가 하락']</t>
+          <t>['상승파동', '대장', '세력']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>142200</v>
+        <v>142500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+4.02%</t>
+          <t>'+4.24%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F11" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G11" t="n">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="H11" t="n">
         <v>15.81</v>
@@ -1438,7 +1438,7 @@
         <v>15.76</v>
       </c>
       <c r="O11" t="n">
-        <v>116682301500</v>
+        <v>118507820900</v>
       </c>
       <c r="P11" t="n">
         <v>164700</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>합병 반대 의견 다수. 정유주 슈퍼 사이클 및 배터리 사업 기대감 속에서도 주가 하락. 윗꼬리 현상 발생.</t>
+          <t>합병 반대 움직임이 강하게 나타나고 있으며, 적자 회사와의 합병 및 시가총액 비율에 대한 의문이 제기됨. 정유 및 배터리 사업의 전망은 긍정적이나, 주가 하락 압력이 지속됨.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['합병', '정유주', '배터리']</t>
+          <t>['합병', '정유', '배터리']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14660</v>
+        <v>14670</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.90%</t>
+          <t>'+3.97%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1530,7 +1530,7 @@
         <v>10.69</v>
       </c>
       <c r="O12" t="n">
-        <v>122434893490</v>
+        <v>123141996125</v>
       </c>
       <c r="P12" t="n">
         <v>23550</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10600</v>
+        <v>10670</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.21%</t>
+          <t>'+3.89%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.26</v>
       </c>
       <c r="E13" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F13" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G13" t="n">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="H13" t="n">
         <v>17.93</v>
@@ -1622,7 +1622,7 @@
         <v>17.67</v>
       </c>
       <c r="O13" t="n">
-        <v>342363030420</v>
+        <v>345375157675</v>
       </c>
       <c r="P13" t="n">
         <v>22450</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15110</v>
+        <v>15060</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+3.07%</t>
+          <t>'+2.73%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-1.17</v>
       </c>
       <c r="E14" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F14" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G14" t="n">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1714,7 +1714,7 @@
         <v>1.17</v>
       </c>
       <c r="O14" t="n">
-        <v>63018057620</v>
+        <v>64087914725</v>
       </c>
       <c r="P14" t="n">
         <v>36200</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>이란 관련 지정학적 이슈로 인한 유가 상승 기대감. 단계적 협상 합의 추진 소식에 주목. 유가 변동에 따른 주가 등락 예상.</t>
+          <t>이란발 지정학적 리스크와 유가 상승 기대감으로 인해 주가 상승 움직임이 관찰됨. 미국과의 단계적 협상 합의 추진 소식이 전해졌으며, 일부에서는 유가 4배 상승 전망을 제시.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['이란', '유가', '지정학적']</t>
+          <t>['유가', '지정학', '이란']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19150</v>
+        <v>19130</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.08%</t>
+          <t>'+1.97%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F15" t="n">
         <v>51</v>
       </c>
       <c r="G15" t="n">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="H15" t="n">
         <v>10.53</v>
@@ -1806,7 +1806,7 @@
         <v>10.55</v>
       </c>
       <c r="O15" t="n">
-        <v>72378360565</v>
+        <v>74314780095</v>
       </c>
       <c r="P15" t="n">
         <v>40350</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17420</v>
+        <v>17370</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.28%</t>
+          <t>'+0.99%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-2.35</v>
       </c>
       <c r="E16" t="n">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F16" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G16" t="n">
-        <v>313</v>
+        <v>340</v>
       </c>
       <c r="H16" t="n">
         <v>0.35</v>
@@ -1898,7 +1898,7 @@
         <v>2.7</v>
       </c>
       <c r="O16" t="n">
-        <v>191880630570</v>
+        <v>193509298745</v>
       </c>
       <c r="P16" t="n">
         <v>30550</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 양자 보안주 급등에 따른 동반 상승 기대. 세계 최초 타이틀 강조. 주포의 움직임에 대한 관찰 및 주가 흐름에 대한 아쉬움 표출.</t>
+          <t>미국 양자 보안주 폭등과 함께 세계 최초 타이틀이 부각되었으나, 주가 흐름은 지지부진한 모습을 보임. 주포의 움직임에 대한 답답함과 함께 상승 모멘텀 부재에 대한 불만이 제기됨.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['양자 보안', '신고가', '주포']</t>
+          <t>['양자보안', '세계최초', '주포']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10030</v>
+        <v>10010</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.40%</t>
+          <t>'+0.20%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F17" t="n">
         <v>53</v>
       </c>
       <c r="G17" t="n">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="H17" t="n">
         <v>0.6</v>
@@ -1990,7 +1990,7 @@
         <v>0.6</v>
       </c>
       <c r="O17" t="n">
-        <v>157134542370</v>
+        <v>157715886325</v>
       </c>
       <c r="P17" t="n">
         <v>15960</v>
@@ -2035,123 +2035,123 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6905</v>
+        <v>248500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.07%</t>
+          <t>'-0.20%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.97</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>68</v>
+        <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>39</v>
+        <v>479</v>
       </c>
       <c r="G18" t="n">
-        <v>133</v>
+        <v>1414</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7</v>
+        <v>46.57</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>6900</v>
+        <v>249000</v>
       </c>
       <c r="K18" t="n">
-        <v>7500</v>
+        <v>248000</v>
       </c>
       <c r="L18" t="n">
-        <v>8190</v>
+        <v>252000</v>
       </c>
       <c r="M18" t="n">
-        <v>6730</v>
+        <v>246000</v>
       </c>
       <c r="N18" t="n">
-        <v>1.67</v>
+        <v>46.64</v>
       </c>
       <c r="O18" t="n">
-        <v>45188181180</v>
+        <v>2261601408000</v>
       </c>
       <c r="P18" t="n">
-        <v>10360</v>
+        <v>374500</v>
       </c>
       <c r="Q18" t="n">
-        <v>2965</v>
+        <v>75900</v>
       </c>
       <c r="R18" t="n">
-        <v>-4000</v>
+        <v>-368000</v>
       </c>
       <c r="S18" t="n">
-        <v>1000</v>
+        <v>-565000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
+          <t>네이버 증권 게시판의 불편함 지적과 함께 정치 관련 논쟁이 혼재. 금리 인상 선반영 기대.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['사이버보안', '양자암호', '공급계약']</t>
+          <t>['금리인상', '네이버증권', '정치']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>106</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>248000</v>
+        <v>1691000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-0.40%</t>
+          <t>'-0.35%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="E19" t="n">
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="G19" t="n">
-        <v>1435</v>
+        <v>1510</v>
       </c>
       <c r="H19" t="n">
-        <v>46.57</v>
+        <v>50.27</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,51 +2159,51 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>249000</v>
+        <v>1697000</v>
       </c>
       <c r="K19" t="n">
-        <v>248000</v>
+        <v>1690000</v>
       </c>
       <c r="L19" t="n">
-        <v>252000</v>
+        <v>1729000</v>
       </c>
       <c r="M19" t="n">
-        <v>246000</v>
+        <v>1671000</v>
       </c>
       <c r="N19" t="n">
-        <v>46.64</v>
+        <v>50.47</v>
       </c>
       <c r="O19" t="n">
-        <v>2153543095000</v>
+        <v>3709973374000</v>
       </c>
       <c r="P19" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q19" t="n">
-        <v>75900</v>
+        <v>325000</v>
       </c>
       <c r="R19" t="n">
-        <v>-368000</v>
+        <v>-297000</v>
       </c>
       <c r="S19" t="n">
-        <v>-565000</v>
+        <v>-104000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>네이버 증권 게시판의 불편함 지적과 함께 정치 관련 논쟁이 혼재. 금리 인상 선반영 기대.</t>
+          <t>AI 및 금리 이슈 등으로 변동성이 큰 가운데, 일부에서는 100만원 하회를 예상하며 부정적인 전망을 제시. 젠슨황의 AI 위험론 사기 발언이 언급되었으나, 전반적인 시장 분위기는 좋지 않음.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['금리인상', '네이버증권', '정치']</t>
+          <t>['AI', '금리', '변동성']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,130 +2212,130 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1683000</v>
+        <v>6870</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-0.82%</t>
+          <t>'-0.43%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.2</v>
+        <v>-0.97</v>
       </c>
       <c r="E20" t="n">
-        <v>800</v>
+        <v>69</v>
       </c>
       <c r="F20" t="n">
-        <v>477</v>
+        <v>40</v>
       </c>
       <c r="G20" t="n">
-        <v>1590</v>
+        <v>133</v>
       </c>
       <c r="H20" t="n">
-        <v>50.27</v>
+        <v>0.7</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>1697000</v>
+        <v>6900</v>
       </c>
       <c r="K20" t="n">
-        <v>1690000</v>
+        <v>7500</v>
       </c>
       <c r="L20" t="n">
-        <v>1729000</v>
+        <v>8190</v>
       </c>
       <c r="M20" t="n">
-        <v>1671000</v>
+        <v>6730</v>
       </c>
       <c r="N20" t="n">
-        <v>50.47</v>
+        <v>1.67</v>
       </c>
       <c r="O20" t="n">
-        <v>3601551227000</v>
+        <v>45359137960</v>
       </c>
       <c r="P20" t="n">
-        <v>2987000</v>
+        <v>10360</v>
       </c>
       <c r="Q20" t="n">
-        <v>325000</v>
+        <v>2965</v>
       </c>
       <c r="R20" t="n">
-        <v>-297000</v>
+        <v>-4000</v>
       </c>
       <c r="S20" t="n">
-        <v>-104000</v>
+        <v>1000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>AI 및 금리 이슈로 인한 변동성 확대. 단기적인 주가 등락에도 불구하고 뚜렷한 방향성 부재. 투자자들의 피로감 누적.</t>
+          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['AI', '금리', '변동성']</t>
+          <t>['사이버보안', '양자암호', '공급계약']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>86200</v>
+        <v>223000</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-0.92%</t>
+          <t>'-0.89%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.11</v>
+        <v>0.15</v>
       </c>
       <c r="E21" t="n">
-        <v>262</v>
+        <v>176</v>
       </c>
       <c r="F21" t="n">
-        <v>140</v>
+        <v>86</v>
       </c>
       <c r="G21" t="n">
-        <v>924</v>
+        <v>980</v>
       </c>
       <c r="H21" t="n">
-        <v>23.45</v>
+        <v>7.2</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,38 +2343,38 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>87000</v>
+        <v>225000</v>
       </c>
       <c r="K21" t="n">
-        <v>86200</v>
+        <v>228500</v>
       </c>
       <c r="L21" t="n">
-        <v>86800</v>
+        <v>229000</v>
       </c>
       <c r="M21" t="n">
-        <v>84200</v>
+        <v>219500</v>
       </c>
       <c r="N21" t="n">
-        <v>23.56</v>
+        <v>7.05</v>
       </c>
       <c r="O21" t="n">
-        <v>135167024150</v>
+        <v>97153058250</v>
       </c>
       <c r="P21" t="n">
-        <v>139200</v>
+        <v>426000</v>
       </c>
       <c r="Q21" t="n">
-        <v>57000</v>
+        <v>89500</v>
       </c>
       <c r="R21" t="n">
-        <v>-220000</v>
+        <v>-120000</v>
       </c>
       <c r="S21" t="n">
-        <v>-152000</v>
+        <v>1000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>원전 사업 기대감과 함께 X에너지 급등. 두산에너빌리티 신용 매수 언급. 원전 ETF 추가 출시.</t>
+          <t>머스크의 테라팹에 패키징 장비 공급 단독 보도. 공매도 세력과의 갈등 양상.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,11 +2383,11 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전', 'X에너지', 'ETF']</t>
+          <t>['패키징', '테라팹', '공매도']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>222500</v>
+        <v>86000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-1.11%</t>
+          <t>'-1.15%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.15</v>
+        <v>-0.11</v>
       </c>
       <c r="E22" t="n">
-        <v>177</v>
+        <v>275</v>
       </c>
       <c r="F22" t="n">
-        <v>87</v>
+        <v>144</v>
       </c>
       <c r="G22" t="n">
-        <v>969</v>
+        <v>932</v>
       </c>
       <c r="H22" t="n">
-        <v>7.2</v>
+        <v>23.45</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,51 +2435,51 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>225000</v>
+        <v>87000</v>
       </c>
       <c r="K22" t="n">
-        <v>228500</v>
+        <v>86200</v>
       </c>
       <c r="L22" t="n">
-        <v>229000</v>
+        <v>86800</v>
       </c>
       <c r="M22" t="n">
-        <v>219500</v>
+        <v>84200</v>
       </c>
       <c r="N22" t="n">
-        <v>7.05</v>
+        <v>23.56</v>
       </c>
       <c r="O22" t="n">
-        <v>94365827500</v>
+        <v>148227615100</v>
       </c>
       <c r="P22" t="n">
-        <v>426000</v>
+        <v>139200</v>
       </c>
       <c r="Q22" t="n">
-        <v>89500</v>
+        <v>57000</v>
       </c>
       <c r="R22" t="n">
-        <v>-120000</v>
+        <v>-220000</v>
       </c>
       <c r="S22" t="n">
-        <v>1000</v>
+        <v>-152000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>머스크의 테라팹에 패키징 장비 공급 단독 보도. 공매도 세력과의 갈등 양상.</t>
+          <t>원전 관련 ETF 추가 출시 및 긍정적인 시나리오가 제시되는 가운데, 엑스에너지의 급등이 두산에너빌리티의 상승 기대감을 높임. 유가 상승에 따른 에너지 독립 필요성이 부각됨.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['패키징', '테라팹', '공매도']</t>
+          <t>['원전', 'ETF', '유가']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8650</v>
+        <v>8670</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-2.26%</t>
+          <t>'-2.03%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="F23" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G23" t="n">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="H23" t="n">
         <v>27.16</v>
@@ -2542,7 +2542,7 @@
         <v>27.16</v>
       </c>
       <c r="O23" t="n">
-        <v>24528452800</v>
+        <v>25094481005</v>
       </c>
       <c r="P23" t="n">
         <v>17950</v>
@@ -2558,16 +2558,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>목표주가 상향 조정에도 불구하고 주가 부진 지속. 연기금 순매수세 관찰되나, 컨센서스 하회 및 실적 부진에 대한 우려 제기.</t>
+          <t>하반기 목표주가 11000원으로 하향 조정된 가운데, 연기금은 순매수를 이어가고 있으나 주가는 3주 연속 음봉을 기록하며 부진한 흐름을 보임. 일부에서는 PBR 평가 방식에 대한 의문을 제기하며 저평가 상태라고 주장.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['목표주가', '실적부진', '연기금']</t>
+          <t>['목표주가', '연기금', 'PBR']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2591,11 +2591,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14120</v>
+        <v>14150</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-2.55%</t>
+          <t>'-2.35%</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -2608,7 +2608,7 @@
         <v>66</v>
       </c>
       <c r="G24" t="n">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="H24" t="n">
         <v>1.8</v>
@@ -2634,7 +2634,7 @@
         <v>1.88</v>
       </c>
       <c r="O24" t="n">
-        <v>62302109700</v>
+        <v>62861238270</v>
       </c>
       <c r="P24" t="n">
         <v>31500</v>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4115</v>
+        <v>4125</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-4.86%</t>
+          <t>'-4.62%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>0.18</v>
       </c>
       <c r="E25" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F25" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G25" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H25" t="n">
         <v>0.77</v>
@@ -2726,7 +2726,7 @@
         <v>0.59</v>
       </c>
       <c r="O25" t="n">
-        <v>73165416066</v>
+        <v>73752340387</v>
       </c>
       <c r="P25" t="n">
         <v>8100</v>
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>20750</v>
+        <v>20850</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-6.11%</t>
+          <t>'-5.66%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.09</v>
       </c>
       <c r="E26" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="F26" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G26" t="n">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="H26" t="n">
         <v>28.9</v>
@@ -2818,7 +2818,7 @@
         <v>28.81</v>
       </c>
       <c r="O26" t="n">
-        <v>71008489575</v>
+        <v>71630703525</v>
       </c>
       <c r="P26" t="n">
         <v>35350</v>

--- a/data/trending_integrated_20260915_14.xlsx
+++ b/data/trending_integrated_20260915_14.xlsx
@@ -578,13 +578,13 @@
         <v>1.34</v>
       </c>
       <c r="E2" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F2" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G2" t="n">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="H2" t="n">
         <v>1.34</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>125215835600</v>
+        <v>125534373680</v>
       </c>
       <c r="P2" t="n">
         <v>5100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>삼성과 4381억 계약 체결 및 광통신, 양자 관련 테마 급등. 시원한 주가 상승세. 추가 상승 기대감 고조.</t>
+          <t>삼성과의 대규모 계약 체결 및 양자/광전자 테마 기대감 속 급등.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['계약 체결', '광통신', '양자 테마']</t>
+          <t>['계약 체결', '양자', '광전자']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.54</v>
       </c>
       <c r="E3" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F3" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G3" t="n">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="H3" t="n">
         <v>3.02</v>
@@ -702,7 +702,7 @@
         <v>3.56</v>
       </c>
       <c r="O3" t="n">
-        <v>65779010685</v>
+        <v>65852812445</v>
       </c>
       <c r="P3" t="n">
         <v>11370</v>
@@ -762,13 +762,13 @@
         <v>-0.31</v>
       </c>
       <c r="E4" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F4" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H4" t="n">
         <v>2.68</v>
@@ -794,7 +794,7 @@
         <v>2.99</v>
       </c>
       <c r="O4" t="n">
-        <v>48631668879</v>
+        <v>48796973489</v>
       </c>
       <c r="P4" t="n">
         <v>8980</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11290</v>
+        <v>11670</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+21.79%</t>
+          <t>'+25.89%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.06</v>
       </c>
       <c r="E5" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="F5" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G5" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H5" t="n">
         <v>1.19</v>
@@ -886,7 +886,7 @@
         <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>193383401310</v>
+        <v>201771537510</v>
       </c>
       <c r="P5" t="n">
         <v>25050</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25050</v>
+        <v>24900</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+14.38%</t>
+          <t>'+13.70%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F6" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G6" t="n">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="H6" t="n">
         <v>4.9</v>
@@ -978,7 +978,7 @@
         <v>4.89</v>
       </c>
       <c r="O6" t="n">
-        <v>220249623775</v>
+        <v>221349420050</v>
       </c>
       <c r="P6" t="n">
         <v>50600</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>50800</v>
+        <v>51100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.28%</t>
+          <t>'+6.90%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.18</v>
       </c>
       <c r="E7" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F7" t="n">
         <v>100</v>
       </c>
       <c r="G7" t="n">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="H7" t="n">
         <v>13.97</v>
@@ -1070,7 +1070,7 @@
         <v>14.15</v>
       </c>
       <c r="O7" t="n">
-        <v>92109780925</v>
+        <v>93013227225</v>
       </c>
       <c r="P7" t="n">
         <v>108900</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>35050</v>
+        <v>35250</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+6.21%</t>
+          <t>'+6.82%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.13</v>
       </c>
       <c r="E8" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F8" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G8" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H8" t="n">
         <v>14.93</v>
@@ -1162,7 +1162,7 @@
         <v>15.06</v>
       </c>
       <c r="O8" t="n">
-        <v>54018597475</v>
+        <v>54628915875</v>
       </c>
       <c r="P8" t="n">
         <v>50400</v>
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32150</v>
+        <v>3625</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.93%</t>
+          <t>'+6.62%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.05</v>
+        <v>0.12</v>
       </c>
       <c r="E9" t="n">
-        <v>182</v>
+        <v>90</v>
       </c>
       <c r="F9" t="n">
-        <v>115</v>
+        <v>51</v>
       </c>
       <c r="G9" t="n">
-        <v>943</v>
+        <v>216</v>
       </c>
       <c r="H9" t="n">
-        <v>17.5</v>
+        <v>0.83</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,91 +1239,91 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>30350</v>
+        <v>3400</v>
       </c>
       <c r="K9" t="n">
-        <v>30250</v>
+        <v>3450</v>
       </c>
       <c r="L9" t="n">
-        <v>32300</v>
+        <v>4080</v>
       </c>
       <c r="M9" t="n">
-        <v>30250</v>
+        <v>3445</v>
       </c>
       <c r="N9" t="n">
-        <v>17.55</v>
+        <v>0.71</v>
       </c>
       <c r="O9" t="n">
-        <v>15567304125</v>
+        <v>154000062135</v>
       </c>
       <c r="P9" t="n">
-        <v>69200</v>
+        <v>4335</v>
       </c>
       <c r="Q9" t="n">
-        <v>24150</v>
+        <v>1246</v>
       </c>
       <c r="R9" t="n">
-        <v>82000</v>
+        <v>-32000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>담관암 치료제 FDA 승인 기대감과 주가 하락세 공존. 기관 및 외인 매도세에 대한 우려. 탐욕과 기다림에 대한 논의.</t>
+          <t>긍정적인 상승 파동 기대감 및 세력 움직임 언급. "날아간다", "대장" 등 긍정적 표현.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['담관암', 'FDA 승인', '주가 하락']</t>
+          <t>['상승파동', '대장', '세력']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3575</v>
+        <v>32300</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+5.15%</t>
+          <t>'+6.43%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.12</v>
+        <v>-0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="F10" t="n">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="G10" t="n">
-        <v>215</v>
+        <v>982</v>
       </c>
       <c r="H10" t="n">
-        <v>0.83</v>
+        <v>17.5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,91 +1331,91 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>3400</v>
+        <v>30350</v>
       </c>
       <c r="K10" t="n">
-        <v>3450</v>
+        <v>30250</v>
       </c>
       <c r="L10" t="n">
-        <v>4080</v>
+        <v>32400</v>
       </c>
       <c r="M10" t="n">
-        <v>3445</v>
+        <v>30250</v>
       </c>
       <c r="N10" t="n">
-        <v>0.71</v>
+        <v>17.55</v>
       </c>
       <c r="O10" t="n">
-        <v>151735871672</v>
+        <v>16863277925</v>
       </c>
       <c r="P10" t="n">
-        <v>4335</v>
+        <v>69200</v>
       </c>
       <c r="Q10" t="n">
-        <v>1246</v>
+        <v>24150</v>
       </c>
       <c r="R10" t="n">
-        <v>-32000</v>
+        <v>82000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>긍정적인 상승 파동 기대감 및 세력 움직임 언급. "날아간다", "대장" 등 긍정적 표현.</t>
+          <t>담관암 치료제 FDA 승인 기대감과 주가 하락세 공존. 기관 및 외인 매도세에 대한 우려. 탐욕과 기다림에 대한 논의.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['상승파동', '대장', '세력']</t>
+          <t>['담관암', 'FDA 승인', '주가 하락']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>142500</v>
+        <v>10760</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+4.24%</t>
+          <t>'+4.77%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.05</v>
+        <v>0.26</v>
       </c>
       <c r="E11" t="n">
-        <v>144</v>
+        <v>197</v>
       </c>
       <c r="F11" t="n">
-        <v>78</v>
+        <v>124</v>
       </c>
       <c r="G11" t="n">
-        <v>341</v>
+        <v>477</v>
       </c>
       <c r="H11" t="n">
-        <v>15.81</v>
+        <v>17.93</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>136700</v>
+        <v>10270</v>
       </c>
       <c r="K11" t="n">
-        <v>139500</v>
+        <v>11000</v>
       </c>
       <c r="L11" t="n">
-        <v>144100</v>
+        <v>11650</v>
       </c>
       <c r="M11" t="n">
-        <v>138200</v>
+        <v>10010</v>
       </c>
       <c r="N11" t="n">
-        <v>15.76</v>
+        <v>17.67</v>
       </c>
       <c r="O11" t="n">
-        <v>118507820900</v>
+        <v>350257058480</v>
       </c>
       <c r="P11" t="n">
-        <v>164700</v>
+        <v>22450</v>
       </c>
       <c r="Q11" t="n">
-        <v>87700</v>
+        <v>1760</v>
       </c>
       <c r="R11" t="n">
-        <v>-3000</v>
+        <v>181000</v>
       </c>
       <c r="S11" t="n">
-        <v>46000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>합병 반대 움직임이 강하게 나타나고 있으며, 적자 회사와의 합병 및 시가총액 비율에 대한 의문이 제기됨. 정유 및 배터리 사업의 전망은 긍정적이나, 주가 하락 압력이 지속됨.</t>
+          <t>아이온큐 급등 및 기타법인 매수세 유입으로 인한 기대감 고조. 트럼프 발언에 따른 AI 성장 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['합병', '정유', '배터리']</t>
+          <t>['아이온큐', 'AI', '기타법인']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14670</v>
+        <v>143000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.97%</t>
+          <t>'+4.61%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>62</v>
+        <v>144</v>
       </c>
       <c r="F12" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="G12" t="n">
-        <v>200</v>
+        <v>346</v>
       </c>
       <c r="H12" t="n">
-        <v>10.75</v>
+        <v>15.81</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,47 +1515,47 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14110</v>
+        <v>136700</v>
       </c>
       <c r="K12" t="n">
-        <v>14110</v>
+        <v>139500</v>
       </c>
       <c r="L12" t="n">
-        <v>15250</v>
+        <v>144100</v>
       </c>
       <c r="M12" t="n">
-        <v>13400</v>
+        <v>138200</v>
       </c>
       <c r="N12" t="n">
-        <v>10.69</v>
+        <v>15.76</v>
       </c>
       <c r="O12" t="n">
-        <v>123141996125</v>
+        <v>120444324900</v>
       </c>
       <c r="P12" t="n">
-        <v>23550</v>
+        <v>164700</v>
       </c>
       <c r="Q12" t="n">
-        <v>5700</v>
+        <v>87700</v>
       </c>
       <c r="R12" t="n">
-        <v>-120000</v>
+        <v>-3000</v>
       </c>
       <c r="S12" t="n">
-        <v>137000</v>
+        <v>46000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>거래량 증가와 함께 15000원 돌파 시도, 주포 움직임에 대한 기대와 우려 혼재.</t>
+          <t>합병 반대 움직임이 강하게 나타나고 있으며, 적자 회사와의 합병 및 시가총액 비율에 대한 의문이 제기됨. 정유 및 배터리 사업의 전망은 긍정적이나, 주가 하락 압력이 지속됨.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['주포', '거래량', '15000원']</t>
+          <t>['합병', '정유', '배터리']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1563,43 +1563,43 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10670</v>
+        <v>14700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.89%</t>
+          <t>'+4.18%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.26</v>
+        <v>0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>188</v>
+        <v>62</v>
       </c>
       <c r="F13" t="n">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="G13" t="n">
-        <v>471</v>
+        <v>201</v>
       </c>
       <c r="H13" t="n">
-        <v>17.93</v>
+        <v>10.75</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,60 +1607,60 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>10270</v>
+        <v>14110</v>
       </c>
       <c r="K13" t="n">
-        <v>11000</v>
+        <v>14110</v>
       </c>
       <c r="L13" t="n">
-        <v>11650</v>
+        <v>15250</v>
       </c>
       <c r="M13" t="n">
-        <v>10010</v>
+        <v>13400</v>
       </c>
       <c r="N13" t="n">
-        <v>17.67</v>
+        <v>10.69</v>
       </c>
       <c r="O13" t="n">
-        <v>345375157675</v>
+        <v>124163760830</v>
       </c>
       <c r="P13" t="n">
-        <v>22450</v>
+        <v>23550</v>
       </c>
       <c r="Q13" t="n">
-        <v>1760</v>
+        <v>5700</v>
       </c>
       <c r="R13" t="n">
-        <v>181000</v>
+        <v>-120000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>137000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>아이온큐 급등 및 기타법인 매수세 유입으로 인한 기대감 고조. 트럼프 발언에 따른 AI 성장 기대.</t>
+          <t>거래량 증가와 함께 15000원 돌파 시도, 주포 움직임에 대한 기대와 우려 혼재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['아이온큐', 'AI', '기타법인']</t>
+          <t>['주포', '거래량', '15000원']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>093370</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15060</v>
+        <v>14980</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.73%</t>
+          <t>'+2.18%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-1.17</v>
       </c>
       <c r="E14" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F14" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G14" t="n">
-        <v>420</v>
+        <v>447</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1714,7 +1714,7 @@
         <v>1.17</v>
       </c>
       <c r="O14" t="n">
-        <v>64087914725</v>
+        <v>65204714610</v>
       </c>
       <c r="P14" t="n">
         <v>36200</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>이란발 지정학적 리스크와 유가 상승 기대감으로 인해 주가 상승 움직임이 관찰됨. 미국과의 단계적 협상 합의 추진 소식이 전해졌으며, 일부에서는 유가 4배 상승 전망을 제시.</t>
+          <t>이란 사태 관련 유가 급등 기대감 속 매수세 유입 및 상승 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['유가', '지정학', '이란']</t>
+          <t>['유가', '이란']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19130</v>
+        <v>19110</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.97%</t>
+          <t>'+1.87%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F15" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G15" t="n">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="H15" t="n">
         <v>10.53</v>
@@ -1806,7 +1806,7 @@
         <v>10.55</v>
       </c>
       <c r="O15" t="n">
-        <v>74314780095</v>
+        <v>75642207330</v>
       </c>
       <c r="P15" t="n">
         <v>40350</v>
@@ -1851,184 +1851,184 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17370</v>
+        <v>10120</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.99%</t>
+          <t>'+1.30%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-2.35</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>215</v>
+        <v>110</v>
       </c>
       <c r="F16" t="n">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="G16" t="n">
-        <v>340</v>
+        <v>170</v>
       </c>
       <c r="H16" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>17200</v>
+        <v>9990</v>
       </c>
       <c r="K16" t="n">
-        <v>17220</v>
+        <v>10110</v>
       </c>
       <c r="L16" t="n">
-        <v>18390</v>
+        <v>11390</v>
       </c>
       <c r="M16" t="n">
-        <v>16600</v>
+        <v>9980</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="O16" t="n">
-        <v>193509298745</v>
+        <v>159898900385</v>
       </c>
       <c r="P16" t="n">
-        <v>30550</v>
+        <v>15960</v>
       </c>
       <c r="Q16" t="n">
-        <v>6100</v>
+        <v>3500</v>
       </c>
       <c r="R16" t="n">
-        <v>-33000</v>
+        <v>-13000</v>
       </c>
       <c r="S16" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 양자 보안주 폭등과 함께 세계 최초 타이틀이 부각되었으나, 주가 흐름은 지지부진한 모습을 보임. 주포의 움직임에 대한 답답함과 함께 상승 모멘텀 부재에 대한 불만이 제기됨.</t>
+          <t>부정적인 언급과 함께 주가 조작 의혹 제기. "저질약품", "최악" 등 부정적 표현 다수.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['양자보안', '세계최초', '주포']</t>
+          <t>['주가조작', '저질약품']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10010</v>
+        <v>17330</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.20%</t>
+          <t>'+0.76%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>-2.35</v>
       </c>
       <c r="E17" t="n">
-        <v>108</v>
+        <v>215</v>
       </c>
       <c r="F17" t="n">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="G17" t="n">
-        <v>168</v>
+        <v>344</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>9990</v>
+        <v>17200</v>
       </c>
       <c r="K17" t="n">
-        <v>10110</v>
+        <v>17220</v>
       </c>
       <c r="L17" t="n">
-        <v>11390</v>
+        <v>18390</v>
       </c>
       <c r="M17" t="n">
-        <v>9980</v>
+        <v>16600</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="O17" t="n">
-        <v>157715886325</v>
+        <v>194251105875</v>
       </c>
       <c r="P17" t="n">
-        <v>15960</v>
+        <v>30550</v>
       </c>
       <c r="Q17" t="n">
-        <v>3500</v>
+        <v>6100</v>
       </c>
       <c r="R17" t="n">
-        <v>-13000</v>
+        <v>-33000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>부정적인 언급과 함께 주가 조작 의혹 제기. "저질약품", "최악" 등 부정적 표현 다수.</t>
+          <t>미국 양자 보안주 테마와 연관된 급등 가능성 언급, 주가 흐름에 대한 아쉬움 표출.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주가조작', '저질약품']</t>
+          <t>['양자 보안', '신고가']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
@@ -2053,10 +2053,10 @@
         <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="G18" t="n">
-        <v>1414</v>
+        <v>1422</v>
       </c>
       <c r="H18" t="n">
         <v>46.57</v>
@@ -2082,7 +2082,7 @@
         <v>46.64</v>
       </c>
       <c r="O18" t="n">
-        <v>2261601408000</v>
+        <v>2364885223500</v>
       </c>
       <c r="P18" t="n">
         <v>374500</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>네이버 증권 게시판의 불편함 지적과 함께 정치 관련 논쟁이 혼재. 금리 인상 선반영 기대.</t>
+          <t>게시판의 불편함과 정치적 이슈 언급, 차트 분석 및 금리 인상 선반영 기대.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['금리인상', '네이버증권', '정치']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1691000</v>
+        <v>1690000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-0.35%</t>
+          <t>'-0.41%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>473</v>
+        <v>459</v>
       </c>
       <c r="G19" t="n">
-        <v>1510</v>
+        <v>1479</v>
       </c>
       <c r="H19" t="n">
         <v>50.27</v>
@@ -2174,7 +2174,7 @@
         <v>50.47</v>
       </c>
       <c r="O19" t="n">
-        <v>3709973374000</v>
+        <v>3811292223500</v>
       </c>
       <c r="P19" t="n">
         <v>2987000</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>AI 및 금리 이슈 등으로 변동성이 큰 가운데, 일부에서는 100만원 하회를 예상하며 부정적인 전망을 제시. 젠슨황의 AI 위험론 사기 발언이 언급되었으나, 전반적인 시장 분위기는 좋지 않음.</t>
+          <t>AI 및 금리 이슈에 대한 혼란 속, 주가 하락에 대한 부정적 전망과 불만 제기.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['AI', '금리', '변동성']</t>
+          <t>['AI', '금리']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2266,7 +2266,7 @@
         <v>1.67</v>
       </c>
       <c r="O20" t="n">
-        <v>45359137960</v>
+        <v>45648731545</v>
       </c>
       <c r="P20" t="n">
         <v>10360</v>
@@ -2311,31 +2311,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>223000</v>
+        <v>86150</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-0.89%</t>
+          <t>'-0.98%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.15</v>
+        <v>-0.11</v>
       </c>
       <c r="E21" t="n">
-        <v>176</v>
+        <v>278</v>
       </c>
       <c r="F21" t="n">
-        <v>86</v>
+        <v>144</v>
       </c>
       <c r="G21" t="n">
-        <v>980</v>
+        <v>939</v>
       </c>
       <c r="H21" t="n">
-        <v>7.2</v>
+        <v>23.45</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,51 +2343,51 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>225000</v>
+        <v>87000</v>
       </c>
       <c r="K21" t="n">
-        <v>228500</v>
+        <v>86200</v>
       </c>
       <c r="L21" t="n">
-        <v>229000</v>
+        <v>86800</v>
       </c>
       <c r="M21" t="n">
-        <v>219500</v>
+        <v>84200</v>
       </c>
       <c r="N21" t="n">
-        <v>7.05</v>
+        <v>23.56</v>
       </c>
       <c r="O21" t="n">
-        <v>97153058250</v>
+        <v>152802513450</v>
       </c>
       <c r="P21" t="n">
-        <v>426000</v>
+        <v>139200</v>
       </c>
       <c r="Q21" t="n">
-        <v>89500</v>
+        <v>57000</v>
       </c>
       <c r="R21" t="n">
-        <v>-120000</v>
+        <v>-220000</v>
       </c>
       <c r="S21" t="n">
-        <v>1000</v>
+        <v>-152000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>머스크의 테라팹에 패키징 장비 공급 단독 보도. 공매도 세력과의 갈등 양상.</t>
+          <t>원전 관련 ETF 추가 출시 및 긍정적인 시나리오가 제시되는 가운데, 엑스에너지의 급등이 두산에너빌리티의 상승 기대감을 높임. 유가 상승에 따른 에너지 독립 필요성이 부각됨.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['패키징', '테라팹', '공매도']</t>
+          <t>['원전', 'ETF', '유가']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>86000</v>
+        <v>222500</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-1.15%</t>
+          <t>'-1.11%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.11</v>
+        <v>0.15</v>
       </c>
       <c r="E22" t="n">
-        <v>275</v>
+        <v>181</v>
       </c>
       <c r="F22" t="n">
-        <v>144</v>
+        <v>89</v>
       </c>
       <c r="G22" t="n">
-        <v>932</v>
+        <v>996</v>
       </c>
       <c r="H22" t="n">
-        <v>23.45</v>
+        <v>7.2</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,51 +2435,51 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>87000</v>
+        <v>225000</v>
       </c>
       <c r="K22" t="n">
-        <v>86200</v>
+        <v>228500</v>
       </c>
       <c r="L22" t="n">
-        <v>86800</v>
+        <v>229000</v>
       </c>
       <c r="M22" t="n">
-        <v>84200</v>
+        <v>219500</v>
       </c>
       <c r="N22" t="n">
-        <v>23.56</v>
+        <v>7.05</v>
       </c>
       <c r="O22" t="n">
-        <v>148227615100</v>
+        <v>98760826750</v>
       </c>
       <c r="P22" t="n">
-        <v>139200</v>
+        <v>426000</v>
       </c>
       <c r="Q22" t="n">
-        <v>57000</v>
+        <v>89500</v>
       </c>
       <c r="R22" t="n">
-        <v>-220000</v>
+        <v>-120000</v>
       </c>
       <c r="S22" t="n">
-        <v>-152000</v>
+        <v>1000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>원전 관련 ETF 추가 출시 및 긍정적인 시나리오가 제시되는 가운데, 엑스에너지의 급등이 두산에너빌리티의 상승 기대감을 높임. 유가 상승에 따른 에너지 독립 필요성이 부각됨.</t>
+          <t>머스크의 테라팹에 패키징 장비 공급 단독 보도. 공매도 세력과의 갈등 양상.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['원전', 'ETF', '유가']</t>
+          <t>['패키징', '테라팹', '공매도']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8670</v>
+        <v>8680</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-2.03%</t>
+          <t>'-1.92%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F23" t="n">
         <v>62</v>
       </c>
       <c r="G23" t="n">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="H23" t="n">
         <v>27.16</v>
@@ -2542,7 +2542,7 @@
         <v>27.16</v>
       </c>
       <c r="O23" t="n">
-        <v>25094481005</v>
+        <v>25412858295</v>
       </c>
       <c r="P23" t="n">
         <v>17950</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14150</v>
+        <v>14160</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-2.35%</t>
+          <t>'-2.28%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.08</v>
       </c>
       <c r="E24" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F24" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G24" t="n">
-        <v>516</v>
+        <v>548</v>
       </c>
       <c r="H24" t="n">
         <v>1.8</v>
@@ -2634,7 +2634,7 @@
         <v>1.88</v>
       </c>
       <c r="O24" t="n">
-        <v>62861238270</v>
+        <v>63465153385</v>
       </c>
       <c r="P24" t="n">
         <v>31500</v>
@@ -2650,16 +2650,16 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>언론 홍보 효과 및 지지 구간 언급. AI, 광전자 관련 테마주로 긍정적 전망.</t>
+          <t>방송 홍보 및 15000원 이상 상승 기대감, 광전자와의 비교 속 키 맞추기 움직임.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['언론홍보', '광통신', 'AI']</t>
+          <t>['대한광통신', '광전자']</t>
         </is>
       </c>
       <c r="X24" t="n">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4125</v>
+        <v>4150</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-4.62%</t>
+          <t>'-4.05%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>0.18</v>
       </c>
       <c r="E25" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F25" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G25" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H25" t="n">
         <v>0.77</v>
@@ -2726,7 +2726,7 @@
         <v>0.59</v>
       </c>
       <c r="O25" t="n">
-        <v>73752340387</v>
+        <v>74439327171</v>
       </c>
       <c r="P25" t="n">
         <v>8100</v>
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>20850</v>
+        <v>20900</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-5.66%</t>
+          <t>'-5.43%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.09</v>
       </c>
       <c r="E26" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F26" t="n">
         <v>133</v>
       </c>
       <c r="G26" t="n">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="H26" t="n">
         <v>28.9</v>
@@ -2818,7 +2818,7 @@
         <v>28.81</v>
       </c>
       <c r="O26" t="n">
-        <v>71630703525</v>
+        <v>72932312600</v>
       </c>
       <c r="P26" t="n">
         <v>35350</v>
